--- a/--Artifact_Development_Tracker.xlsx
+++ b/--Artifact_Development_Tracker.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L163"/>
+  <dimension ref="A1:L164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>PSAP Cybersecurity Program   |   Artifact Development Tracker   |   161 Total Artifacts</t>
+          <t>PSAP Cybersecurity Program   |   Artifact Development Tracker   |   162 Total Artifacts</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="J3" s="15" t="inlineStr">
         <is>
-          <t>Draft - In Progress</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="K3" s="17" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="J4" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="K4" s="17" t="inlineStr">
@@ -758,7 +758,11 @@
           <t>Authorizes the program and names its sponsor: program name, scope, authorizing official, and committed resources. Designates the cybersecurity and privacy lead for the ECC/PSAP and confirms the director's authority to direct IT resources (county, contracted, or in-house) toward security work. Includes a short strategic-objectives statement. Signed by executive leadership.</t>
         </is>
       </c>
-      <c r="L4" s="17" t="n"/>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>Uses SHELL-Policy-Charter.docx (charter variant of the Policy shell).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -785,12 +789,12 @@
       <c r="F5" s="15" t="n"/>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>Risk Management Methodology Document</t>
+          <t>Risk Management Methodology Standard</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
@@ -800,15 +804,19 @@
       </c>
       <c r="J5" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t>Documents how risk is managed: risk appetite/tolerance, how risks are identified and scored, the threat vectors covered (phishing, malware, supplier, denial-of-service), and assessment scope, frequency, roles, and methods. Serves as the risk-assessment SOP and includes an explicit risk-appetite statement. Reviewed on a set schedule.</t>
-        </is>
-      </c>
-      <c r="L5" s="17" t="n"/>
+          <t>The governing standard for risk management: the risk appetite and tolerance statement, the impact and likelihood scales and rating thresholds, and the threat vectors in scope (phishing, malware, supplier, denial-of-service). Sets the approach and appetite; the step-by-step assessment runs in the Risk Assessment Procedure (A-172). Reviewed on a set schedule.</t>
+        </is>
+      </c>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t>Split 2026-06-03: retyped Policy-&gt;Standard and renamed from Risk Management Methodology Document; the SOP half became A-172 Risk Assessment Procedure. Classified Internal under the Standard drop rule. Satisfies 1D-1. Form drafted.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -828,41 +836,45 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>A-023</t>
+          <t>A-172</t>
         </is>
       </c>
       <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>A-009</t>
+          <t>A-032</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>Board / Leadership Security Reporting Template</t>
+          <t>Risk Assessment Procedure</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>Report / Assessment</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
         <is>
-          <t>Recurring report rolling up program status, metrics, open findings, and risk decisions for the board or leadership. The wrapper for Phase 2 findings; high visibility, short to produce.</t>
-        </is>
-      </c>
-      <c r="L6" s="17" t="n"/>
+          <t>The repeatable steps for running a risk assessment: scope-setting, threat and failure-mode identification, likelihood and impact scoring against the scales in the Risk Management Methodology Standard, rating against appetite, and recording results. Implements the Standard (A-032) and produces the Risk Assessment Report (A-008). Covers assessment frequency, roles per step, and verification.</t>
+        </is>
+      </c>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t>Created 2026-06-03 as the SOP half split from the former Risk Management Methodology Document. Depends on A-032. Satisfies 1D-3 and the risk-assessment item in 1C-5. Appended at T1-29/#162 (no renumber); confirm desired Tier/Seq placement. Form drafted.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -882,28 +894,28 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>A-027</t>
+          <t>A-023</t>
         </is>
       </c>
       <c r="E7" s="15" t="n"/>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>A-001</t>
+          <t>A-009</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>Cybersecurity Budget &amp; Resource Allocation Record</t>
+          <t>Board / Leadership Security Reporting Template</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Report / Assessment</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
@@ -913,7 +925,7 @@
       </c>
       <c r="K7" s="17" t="inlineStr">
         <is>
-          <t>Records the dedicated security budget line or allocation with a named owner, and the staffing, tooling, and funding committed each cycle. Ties spend back to the Charter. Dated entries support the annual leadership review.</t>
+          <t>Recurring report rolling up program status, metrics, open findings, and risk decisions for the board or leadership. The wrapper for Phase 2 findings; high visibility, short to produce.</t>
         </is>
       </c>
       <c r="L7" s="17" t="n"/>
@@ -936,7 +948,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>A-028</t>
+          <t>A-027</t>
         </is>
       </c>
       <c r="E8" s="15" t="n"/>
@@ -947,27 +959,27 @@
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>Leadership Security Review Meeting Minutes</t>
+          <t>Cybersecurity Budget &amp; Resource Allocation Record</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Financial Ledger</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="K8" s="17" t="inlineStr">
         <is>
-          <t>Recurring record of leadership review: attendees, program status, metrics and risks reviewed, and resulting decisions or priorities. Evidence that senior leaders review the program and emerging threats on a set cadence.</t>
+          <t>Records the dedicated security budget line or allocation with a named owner, and the staffing, tooling, and funding committed each cycle. Ties spend back to the Charter. Dated entries support the annual leadership review.</t>
         </is>
       </c>
       <c r="L8" s="17" t="n"/>
@@ -990,7 +1002,7 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>A-091</t>
+          <t>A-028</t>
         </is>
       </c>
       <c r="E9" s="15" t="n"/>
@@ -1001,27 +1013,27 @@
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>Threat Intelligence Routing &amp; Distribution Matrix</t>
+          <t>Leadership Security Review Meeting Minutes</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>Reference Matrix</t>
+          <t>Meeting Minutes</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="K9" s="17" t="inlineStr">
         <is>
-          <t>Maps threat-intelligence sources to recipients and actions: which feeds and partnerships the PSAP subscribes to (e.g., MS-ISAC, EI-ISAC, CISA, Indiana IOT), who receives each, the cadence, and the escalation path into the Incident Notification &amp; Escalation Contact List.</t>
+          <t>Recurring record of leadership review: attendees, program status, metrics and risks reviewed, and resulting decisions or priorities. Evidence that senior leaders review the program and emerging threats on a set cadence.</t>
         </is>
       </c>
       <c r="L9" s="17" t="n"/>
@@ -1044,28 +1056,28 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>A-003</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
+          <t>A-091</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>A-001</t>
+        </is>
+      </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>Master Asset Inventory</t>
+          <t>Threat Intelligence Routing &amp; Distribution Matrix</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Reference Matrix</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
@@ -1075,7 +1087,7 @@
       </c>
       <c r="K10" s="17" t="inlineStr">
         <is>
-          <t>Authoritative register of every hardware, software, and firmware asset: make/model, version, owner, location, connectivity. Includes an endpoint-detail view (OS, patch level, endpoint security agent, last seen) for workstations, servers, and mobile endpoints. Feeds backup scope, logging scope, encryption decisions, and the criticality ranking. Kept current on a set cadence.</t>
+          <t>Maps threat-intelligence sources to recipients and actions: which feeds and partnerships the PSAP subscribes to (e.g., MS-ISAC, EI-ISAC, CISA, Indiana IOT), who receives each, the cadence, and the escalation path into the Incident Notification &amp; Escalation Contact List.</t>
         </is>
       </c>
       <c r="L10" s="17" t="n"/>
@@ -1098,7 +1110,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>A-004</t>
+          <t>A-003</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1106,14 +1118,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>A-003</t>
-        </is>
-      </c>
+      <c r="F11" s="15" t="n"/>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>Asset Criticality Ranking Matrix</t>
+          <t>Master Asset Inventory</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
@@ -1133,7 +1141,7 @@
       </c>
       <c r="K11" s="17" t="inlineStr">
         <is>
-          <t>Scores or tiers each asset from the Master Asset Inventory by operational importance to 9-1-1 call handling (e.g., Critical / Important / Supporting), considering confidentiality, integrity, and availability. Drives RTO/RPO targets, backup priority, logging scope, and encryption tiering. Separates the criticality decision from the inventory exercise.</t>
+          <t>Authoritative register of every hardware, software, and firmware asset: make/model, version, owner, location, connectivity. Includes an endpoint-detail view (OS, patch level, endpoint security agent, last seen) for workstations, servers, and mobile endpoints. Feeds backup scope, logging scope, encryption decisions, and the criticality ranking. Kept current on a set cadence.</t>
         </is>
       </c>
       <c r="L11" s="17" t="n"/>
@@ -1156,28 +1164,32 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>A-029</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="n"/>
+          <t>A-004</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>A-002</t>
+          <t>A-003</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>Policy Review &amp; Approval Log</t>
+          <t>Asset Criticality Ranking Matrix</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
@@ -1187,7 +1199,7 @@
       </c>
       <c r="K12" s="17" t="inlineStr">
         <is>
-          <t>Tracks each policy's version, review date, reviewer/approver, and summary of change across the policy library. Evidence that policies are reviewed and re-approved on schedule. Starts once policies exist.</t>
+          <t>Scores or tiers each asset from the Master Asset Inventory by operational importance to 9-1-1 call handling (e.g., Critical / Important / Supporting), considering confidentiality, integrity, and availability. Drives RTO/RPO targets, backup priority, logging scope, and encryption tiering. Separates the criticality decision from the inventory exercise.</t>
         </is>
       </c>
       <c r="L12" s="17" t="n"/>
@@ -1210,28 +1222,28 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>A-092</t>
+          <t>A-029</t>
         </is>
       </c>
       <c r="E13" s="15" t="n"/>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>A-003</t>
+          <t>A-002</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>System Security Plans (per critical system)</t>
+          <t>Policy Review &amp; Approval Log</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
@@ -1241,7 +1253,7 @@
       </c>
       <c r="K13" s="17" t="inlineStr">
         <is>
-          <t>One plan per critical system (CAD, CPE/CHE, GIS, logging, mapping): assigns roles and responsibilities, records categorization by importance and data sensitivity, describes how the system connects and exchanges data, and lists the controls in place. Updated after each risk review. Draws system identity from the Master Asset Inventory and tier from the Criticality Ranking Matrix.</t>
+          <t>Tracks each policy's version, review date, reviewer/approver, and summary of change across the policy library. Evidence that policies are reviewed and re-approved on schedule. Starts once policies exist.</t>
         </is>
       </c>
       <c r="L13" s="17" t="n"/>
@@ -1264,28 +1276,28 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>A-006</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="n"/>
+          <t>A-092</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>A-003</t>
+        </is>
+      </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>IT Support Accountability Agreement (SLA / MOU)</t>
+          <t>System Security Plans (per critical system)</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>Agreement / Form</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
@@ -1295,7 +1307,7 @@
       </c>
       <c r="K14" s="17" t="inlineStr">
         <is>
-          <t>Written cybersecurity obligations between the PSAP and its IT provider (county IT, contractor, or in-house): security responsibilities, response and restoration expectations, patching and monitoring duties, breach-notification timing, and points of contact. The enforcement mechanism behind governance. Pairs with the RACI.</t>
+          <t>One plan per critical system (CAD, CPE/CHE, GIS, logging, mapping): assigns roles and responsibilities, records categorization by importance and data sensitivity, describes how the system connects and exchanges data, and lists the controls in place. Updated after each risk review. Draws system identity from the Master Asset Inventory and tier from the Criticality Ranking Matrix.</t>
         </is>
       </c>
       <c r="L14" s="17" t="n"/>
@@ -1318,7 +1330,7 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>A-010</t>
+          <t>A-006</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -1329,17 +1341,17 @@
       <c r="F15" s="15" t="n"/>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>Access Control Policy</t>
+          <t>IT Support Accountability Agreement (SLA / MOU)</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Agreement / Form</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>Internal / CJIS</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
@@ -1349,7 +1361,7 @@
       </c>
       <c r="K15" s="17" t="inlineStr">
         <is>
-          <t>Defines who may access which systems, under what conditions, and through what approval process, covering user, admin, service, cloud, vendor, and remote accounts. Includes a Service &amp; Cloud Accounts section (owner, purpose, lifespan, least-privilege scope, review cadence for each non-human account). Sets least privilege as the default; names the owning governance body and review cadence. CJIS/IDACS access governed in addition. Cross-refs the Access Entitlement Matrix and the provisioning/deprovisioning workflow.</t>
+          <t>Written cybersecurity obligations between the PSAP and its IT provider (county IT, contractor, or in-house): security responsibilities, response and restoration expectations, patching and monitoring duties, breach-notification timing, and points of contact. The enforcement mechanism behind governance. Pairs with the RACI.</t>
         </is>
       </c>
       <c r="L15" s="17" t="n"/>
@@ -1372,7 +1384,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>A-012</t>
+          <t>A-010</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -1383,7 +1395,7 @@
       <c r="F16" s="15" t="n"/>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>Data Classification Policy</t>
+          <t>Access Control Policy</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -1393,7 +1405,7 @@
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal / CJIS</t>
         </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
@@ -1403,7 +1415,7 @@
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>Defines the classification tiers (Internal, Restricted, Confidential, aligned to the NENA NG-SEC taxonomy) and the PSAP data types mapped to each, with default labels and the minimum protection required at each tier. The parent for encryption, retention, disposal, and the data map. Reviewed as data types and regulations change.</t>
+          <t>Defines who may access which systems, under what conditions, and through what approval process, covering user, admin, service, cloud, vendor, and remote accounts. Includes a Service &amp; Cloud Accounts section (owner, purpose, lifespan, least-privilege scope, review cadence for each non-human account). Sets least privilege as the default; names the owning governance body and review cadence. CJIS/IDACS access governed in addition. Cross-refs the Access Entitlement Matrix and the provisioning/deprovisioning workflow.</t>
         </is>
       </c>
       <c r="L16" s="17" t="n"/>
@@ -1426,7 +1438,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>A-014</t>
+          <t>A-012</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -1437,17 +1449,17 @@
       <c r="F17" s="15" t="n"/>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>Incident Response Plan (IRP)</t>
+          <t>Data Classification Policy</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>Restricted / CJIS</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
@@ -1457,7 +1469,7 @@
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>PSAP-specific incident response: declaration, command structure, roles, containment, and resolution, built around the constraint that 9-1-1 call handling cannot stop. Defines how teams communicate and escalate for all public-safety systems. The anchor for forensics, tabletop, continuity, and data-incident artifacts; embedded in staff training. Reviewed annually; CJIS and HEA 1169 reporting referenced.</t>
+          <t>Defines the classification tiers (Internal, Restricted, Confidential, aligned to the NENA NG-SEC taxonomy) and the PSAP data types mapped to each, with default labels and the minimum protection required at each tier. The parent for encryption, retention, disposal, and the data map. Reviewed as data types and regulations change.</t>
         </is>
       </c>
       <c r="L17" s="17" t="n"/>
@@ -1480,7 +1492,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>A-024</t>
+          <t>A-014</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
@@ -1491,17 +1503,17 @@
       <c r="F18" s="15" t="n"/>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>Acceptable Use Policy (AUP)</t>
+          <t>Incident Response Plan (IRP)</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted / CJIS</t>
         </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
@@ -1511,7 +1523,7 @@
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
-          <t>Permitted and prohibited use of PSAP systems, networks, and data, including personal-device, social-media, credential-protection, logoff, and remote-access expectations, signed before access. Includes a System Use Notification / Login Banner section (approved banner text, where it applies, and consent logging). Renewed at least annually.</t>
+          <t>PSAP-specific incident response: declaration, command structure, roles, containment, and resolution, built around the constraint that 9-1-1 call handling cannot stop. Defines how teams communicate and escalate for all public-safety systems. The anchor for forensics, tabletop, continuity, and data-incident artifacts; embedded in staff training. Reviewed annually; CJIS and HEA 1169 reporting referenced.</t>
         </is>
       </c>
       <c r="L18" s="17" t="n"/>
@@ -1534,7 +1546,7 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>A-057</t>
+          <t>A-024</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -1542,14 +1554,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
-        <is>
-          <t>A-003</t>
-        </is>
-      </c>
+      <c r="F19" s="15" t="n"/>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>Logging Policy</t>
+          <t>Acceptable Use Policy (AUP)</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
@@ -1569,7 +1577,7 @@
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
-          <t>Defines which systems must log, what event types and fields to capture (time, account, success/failure, data accessed), minimum retention, and who is responsible for generation, protection, review, and analysis, scaled to each system's importance. Scope set by the asset inventory. The parent for retention, review, and monitoring artifacts.</t>
+          <t>Permitted and prohibited use of PSAP systems, networks, and data, including personal-device, social-media, credential-protection, logoff, and remote-access expectations, signed before access. Includes a System Use Notification / Login Banner section (approved banner text, where it applies, and consent logging). Renewed at least annually.</t>
         </is>
       </c>
       <c r="L19" s="17" t="n"/>
@@ -1592,14 +1600,22 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>A-007</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
+          <t>A-057</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>A-003</t>
+        </is>
+      </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>Cybersecurity Governance Charter</t>
+          <t>Logging Policy</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
@@ -1619,7 +1635,7 @@
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>Establishes the governance body (steering committee or board) empowered to set security and privacy priorities, review metrics and reports, and ensure alignment with public-safety goals and legal requirements. Names the executive sponsor, the body's membership, and its meeting cadence.</t>
+          <t>Defines which systems must log, what event types and fields to capture (time, account, success/failure, data accessed), minimum retention, and who is responsible for generation, protection, review, and analysis, scaled to each system's importance. Scope set by the asset inventory. The parent for retention, review, and monitoring artifacts.</t>
         </is>
       </c>
       <c r="L20" s="17" t="n"/>
@@ -1642,19 +1658,19 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>A-005</t>
+          <t>A-007</t>
         </is>
       </c>
       <c r="E21" s="15" t="n"/>
       <c r="F21" s="15" t="n"/>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>RACI Matrix for Cybersecurity</t>
+          <t>Cybersecurity Governance Charter</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>Reference Matrix</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
@@ -1669,10 +1685,14 @@
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>Maps each major security function to who is Responsible, Accountable, Consulted, and Informed, across PSAP staff, county/contracted IT, and vendors. The reference that defines who owns and executes every other artifact. Reviewed annually.</t>
-        </is>
-      </c>
-      <c r="L21" s="17" t="n"/>
+          <t>Establishes the governance body (steering committee or board) empowered to set security and privacy priorities, review metrics and reports, and ensure alignment with public-safety goals and legal requirements. Names the executive sponsor, the body's membership, and its meeting cadence.</t>
+        </is>
+      </c>
+      <c r="L21" s="17" t="inlineStr">
+        <is>
+          <t>Uses SHELL-Policy-Charter.docx (charter variant of the Policy shell).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -1692,23 +1712,19 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>A-030</t>
+          <t>A-005</t>
         </is>
       </c>
       <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>A-005</t>
-        </is>
-      </c>
+      <c r="F22" s="15" t="n"/>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>Security Role Descriptions</t>
+          <t>RACI Matrix for Cybersecurity</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Reference Matrix</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
@@ -1723,7 +1739,7 @@
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>Formal descriptions of each security-relevant role (title, duties, required screening/training, reporting line), extending the RACI into job-description detail. Confirms enough trained personnel, internal or contracted, to configure securely, monitor, respond, and audit.</t>
+          <t>Maps each major security function to who is Responsible, Accountable, Consulted, and Informed, across PSAP staff, county/contracted IT, and vendors. The reference that defines who owns and executes every other artifact. Reviewed annually.</t>
         </is>
       </c>
       <c r="L22" s="17" t="n"/>
@@ -1746,23 +1762,23 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>A-031</t>
+          <t>A-030</t>
         </is>
       </c>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>A-007</t>
+          <t>A-005</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>Governance Reporting Calendar</t>
+          <t>Security Role Descriptions</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
@@ -1777,7 +1793,7 @@
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>Operationalizes the Governance Charter: what reports and reviews are due, to whom, and how often (leadership reviews, metrics, policy reviews, board reporting). Lists item, frequency, next due, owner, last completed, with escalation for missed items.</t>
+          <t>Formal descriptions of each security-relevant role (title, duties, required screening/training, reporting line), extending the RACI into job-description detail. Confirms enough trained personnel, internal or contracted, to configure securely, monitor, respond, and audit.</t>
         </is>
       </c>
       <c r="L23" s="17" t="n"/>
@@ -1800,28 +1816,28 @@
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>A-043</t>
+          <t>A-031</t>
         </is>
       </c>
       <c r="E24" s="15" t="n"/>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>A-012</t>
+          <t>A-007</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>Data Inventory / Data Map</t>
+          <t>Governance Reporting Calendar</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>Restricted / CJIS</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
@@ -1831,7 +1847,7 @@
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>Maps each data type to its owning system, classification, and lifecycle. Includes control-mapping columns: for each data category, the encryption mechanism, access-restriction method, and retention reference (the as-built protection control). Reconciled on a set cadence.</t>
+          <t>Operationalizes the Governance Charter: what reports and reviews are due, to whom, and how often (leadership reviews, metrics, policy reviews, board reporting). Lists item, frequency, next due, owner, last completed, with escalation for missed items.</t>
         </is>
       </c>
       <c r="L24" s="17" t="n"/>
@@ -1854,18 +1870,18 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>A-083</t>
+          <t>A-043</t>
         </is>
       </c>
       <c r="E25" s="15" t="n"/>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>A-009</t>
+          <t>A-012</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>Risk / Finding Register (POA&amp;M)</t>
+          <t>Data Inventory / Data Map</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
@@ -1875,7 +1891,7 @@
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Restricted / CJIS</t>
         </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
@@ -1885,7 +1901,7 @@
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>Consolidated POA&amp;M: all findings from assessments, scans, and audits with source, owner, due date, and status, tracked to closure. Boundary: holds assessment/audit findings; enterprise risks live in the Risk Register. Prioritizes by life-safety and service-continuity impact.</t>
+          <t>Maps each data type to its owning system, classification, and lifecycle. Includes control-mapping columns: for each data category, the encryption mechanism, access-restriction method, and retention reference (the as-built protection control). Reconciled on a set cadence.</t>
         </is>
       </c>
       <c r="L25" s="17" t="n"/>
@@ -1908,23 +1924,23 @@
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>A-117</t>
+          <t>A-083</t>
         </is>
       </c>
       <c r="E26" s="15" t="n"/>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>A-052</t>
+          <t>A-009</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>System Configuration Baselines (per system type)</t>
+          <t>Risk / Finding Register (POA&amp;M)</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
@@ -1939,7 +1955,7 @@
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>Approved secure configuration per device/system type (workstations, servers, network devices, telephony/CAD appliances): password rules, open/closed ports, logging, and deliberate modifications from vendor defaults. Confirms SBC consoles are covered as a system type, including lockout settings. Network zones and ACLs documented here and change-controlled.</t>
+          <t>Consolidated POA&amp;M: all findings from assessments, scans, and audits with source, owner, due date, and status, tracked to closure. Boundary: holds assessment/audit findings; enterprise risks live in the Risk Register. Prioritizes by life-safety and service-continuity impact.</t>
         </is>
       </c>
       <c r="L26" s="17" t="n"/>
@@ -1962,24 +1978,28 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>A-155</t>
+          <t>A-117</t>
         </is>
       </c>
       <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>A-052</t>
+        </is>
+      </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>Background Check &amp; Screening Policy</t>
+          <t>System Configuration Baselines (per system type)</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>Internal / CJIS</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
@@ -1989,7 +2009,7 @@
       </c>
       <c r="K27" s="17" t="inlineStr">
         <is>
-          <t>Which positions require pre-employment background checks, the scope of the check, adjudication of findings, and the vetting required for contractors and vendor personnel with unescorted access to controlled areas or ECC/NG9-1-1 systems. CJIS screening applies where in scope.</t>
+          <t>Approved secure configuration per device/system type (workstations, servers, network devices, telephony/CAD appliances): password rules, open/closed ports, logging, and deliberate modifications from vendor defaults. Confirms SBC consoles are covered as a system type, including lockout settings. Network zones and ACLs documented here and change-controlled.</t>
         </is>
       </c>
       <c r="L27" s="17" t="n"/>
@@ -2012,28 +2032,24 @@
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>A-009</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>A-155</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="n"/>
       <c r="F28" s="15" t="n"/>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>Risk Register</t>
+          <t>Background Check &amp; Screening Policy</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal / CJIS</t>
         </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
@@ -2043,7 +2059,7 @@
       </c>
       <c r="K28" s="17" t="inlineStr">
         <is>
-          <t>Active log of identified risks: description, likelihood, impact, treatment decision, owner, review date. Parent that the Risk / Finding Register (POA&amp;M) feeds into. Boundary: holds enterprise/strategic risks; assessment findings tracked to closure live in the Risk / Finding Register, and current treatment state references the Risk Treatment / Acceptance Decisions Log rather than restating it. Grows through all phases.</t>
+          <t>Which positions require pre-employment background checks, the scope of the check, adjudication of findings, and the vetting required for contractors and vendor personnel with unescorted access to controlled areas or ECC/NG9-1-1 systems. CJIS screening applies where in scope.</t>
         </is>
       </c>
       <c r="L28" s="17" t="n"/>
@@ -2066,23 +2082,23 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>A-008</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>A-032</t>
-        </is>
-      </c>
+          <t>A-009</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n"/>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t>Risk Assessment Report</t>
+          <t>Risk Register</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>Report / Assessment</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I29" s="17" t="inlineStr">
@@ -2097,7 +2113,7 @@
       </c>
       <c r="K29" s="17" t="inlineStr">
         <is>
-          <t>Documents each formal risk assessment: scope (which public-safety systems), method (interviews, scans, tabletop), threats and failure modes considered, and impact scoring on service, data, and life safety. Scope explicitly names facility and environmental hazards (fire, flood, temperature, utility, EMP). Provides the evidence base for prioritization; feeds the Risk Register.</t>
+          <t>Active log of identified risks: description, likelihood, impact, treatment decision, owner, review date. Parent that the Risk / Finding Register (POA&amp;M) feeds into. Boundary: holds enterprise/strategic risks; assessment findings tracked to closure live in the Risk / Finding Register, and current treatment state references the Risk Treatment / Acceptance Decisions Log rather than restating it. Grows through all phases.</t>
         </is>
       </c>
       <c r="L29" s="17" t="n"/>
@@ -2120,23 +2136,23 @@
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>A-033</t>
+          <t>A-008</t>
         </is>
       </c>
       <c r="E30" s="15" t="n"/>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>A-009</t>
+          <t>A-172</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>Risk Treatment / Acceptance Decisions Log</t>
+          <t>Risk Assessment Report</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Report / Assessment</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
@@ -2151,10 +2167,14 @@
       </c>
       <c r="K30" s="17" t="inlineStr">
         <is>
-          <t>Dated record of risk-treatment and risk-acceptance decisions: the risk, the decision (mitigate/accept/transfer), who decided, the rationale, and the review date. Boundary: the decision record; the Risk Register references it for current treatment state.</t>
-        </is>
-      </c>
-      <c r="L30" s="17" t="n"/>
+          <t>Documents each formal risk assessment: scope (which public-safety systems), method (interviews, scans, tabletop), threats and failure modes considered, and impact scoring on service, data, and life safety. Scope explicitly names facility and environmental hazards (fire, flood, temperature, utility, EMP). Provides the evidence base for prioritization; feeds the Risk Register.</t>
+        </is>
+      </c>
+      <c r="L30" s="17" t="inlineStr">
+        <is>
+          <t>Depends repointed A-032-&gt;A-172 (2026-06-03): the report is the output of running the Risk Assessment Procedure.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -2164,38 +2184,38 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>T2-01</t>
+          <t>T1-29</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>A-044</t>
+          <t>A-033</t>
         </is>
       </c>
       <c r="E31" s="15" t="n"/>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>A-012</t>
+          <t>A-009</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
-          <t>Data Retention Schedule</t>
+          <t>Risk Treatment / Acceptance Decisions Log</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
@@ -2205,7 +2225,7 @@
       </c>
       <c r="K31" s="17" t="inlineStr">
         <is>
-          <t>By data category, the minimum and maximum retention periods and the regulatory or operational basis for each. Requires the Data Classification Policy as input; drives disposal. Lists item, period, basis, owner, next review.</t>
+          <t>Dated record of risk-treatment and risk-acceptance decisions: the risk, the decision (mitigate/accept/transfer), who decided, the rationale, and the review date. Boundary: the decision record; the Risk Register references it for current treatment state.</t>
         </is>
       </c>
       <c r="L31" s="17" t="n"/>
@@ -2223,12 +2243,12 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>T2-02</t>
+          <t>T2-01</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>A-099</t>
+          <t>A-044</t>
         </is>
       </c>
       <c r="E32" s="15" t="n"/>
@@ -2239,12 +2259,12 @@
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>Data Labeling Procedures</t>
+          <t>Data Retention Schedule</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
@@ -2259,7 +2279,7 @@
       </c>
       <c r="K32" s="17" t="inlineStr">
         <is>
-          <t>How labels are applied and maintained: default labels on new or incoming data, classification of external data on receipt, label review when data moves across departments or to partners, and how labels drive system controls. Steps and roles per the Data Classification Policy.</t>
+          <t>By data category, the minimum and maximum retention periods and the regulatory or operational basis for each. Requires the Data Classification Policy as input; drives disposal. Lists item, period, basis, owner, next review.</t>
         </is>
       </c>
       <c r="L32" s="17" t="n"/>
@@ -2277,12 +2297,12 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>T2-03</t>
+          <t>T2-02</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>A-102</t>
+          <t>A-099</t>
         </is>
       </c>
       <c r="E33" s="15" t="n"/>
@@ -2293,12 +2313,12 @@
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>Data Access Monitoring Policy</t>
+          <t>Data Labeling Procedures</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I33" s="17" t="inlineStr">
@@ -2313,7 +2333,7 @@
       </c>
       <c r="K33" s="17" t="inlineStr">
         <is>
-          <t>Requires logging of access to and attempted disclosure of sensitive data (who, when, from where, what action), retention long enough for audits and investigations, and enforcement of label-based access controls with logged denials. Scoped to data-access events; general logging governed by the Logging Policy.</t>
+          <t>How labels are applied and maintained: default labels on new or incoming data, classification of external data on receipt, label review when data moves across departments or to partners, and how labels drive system controls. Steps and roles per the Data Classification Policy.</t>
         </is>
       </c>
       <c r="L33" s="17" t="n"/>
@@ -2331,19 +2351,23 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>T2-04</t>
+          <t>T2-03</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>A-069</t>
+          <t>A-102</t>
         </is>
       </c>
       <c r="E34" s="15" t="n"/>
-      <c r="F34" s="15" t="n"/>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>A-012</t>
+        </is>
+      </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>Physical Access Control Policy</t>
+          <t>Data Access Monitoring Policy</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
@@ -2363,7 +2387,7 @@
       </c>
       <c r="K34" s="17" t="inlineStr">
         <is>
-          <t>Defines which facility areas require controlled access, the authorization mechanism (badge, key, PIN, biometric), who may grant access, and credential issue/revocation. Includes a visitor management section (authorization before arrival, identity verification, badge issuance and tracking, escort requirements). Covers IDF/MDF closets, server rooms, and cable pathways at the same standard. Reviewed on a set cadence.</t>
+          <t>Requires logging of access to and attempted disclosure of sensitive data (who, when, from where, what action), retention long enough for audits and investigations, and enforcement of label-based access controls with logged denials. Scoped to data-access events; general logging governed by the Logging Policy.</t>
         </is>
       </c>
       <c r="L34" s="17" t="n"/>
@@ -2381,33 +2405,29 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>T2-05</t>
+          <t>T2-04</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>A-070</t>
+          <t>A-069</t>
         </is>
       </c>
       <c r="E35" s="15" t="n"/>
-      <c r="F35" s="15" t="inlineStr">
-        <is>
-          <t>A-069</t>
-        </is>
-      </c>
+      <c r="F35" s="15" t="n"/>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>Access Authorization List</t>
+          <t>Physical Access Control Policy</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
@@ -2417,7 +2437,7 @@
       </c>
       <c r="K35" s="17" t="inlineStr">
         <is>
-          <t>Current list of individuals authorized to access each controlled area (dispatch floor, equipment room, server room, IT closet), with the key/badge issuance and deprovisioning record. Maintained per the Physical Access Control Policy.</t>
+          <t>Defines which facility areas require controlled access, the authorization mechanism (badge, key, PIN, biometric), who may grant access, and credential issue/revocation. Includes a visitor management section (authorization before arrival, identity verification, badge issuance and tracking, escort requirements). Covers IDF/MDF closets, server rooms, and cable pathways at the same standard. Reviewed on a set cadence.</t>
         </is>
       </c>
       <c r="L35" s="17" t="n"/>
@@ -2435,12 +2455,12 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>T2-06</t>
+          <t>T2-05</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>A-148</t>
+          <t>A-070</t>
         </is>
       </c>
       <c r="E36" s="15" t="n"/>
@@ -2451,17 +2471,17 @@
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>Controlled Area / Zone Map</t>
+          <t>Access Authorization List</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>Architecture / Design</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
@@ -2471,7 +2491,7 @@
       </c>
       <c r="K36" s="17" t="inlineStr">
         <is>
-          <t>Diagram of the facility's controlled areas and security zones, the access level for each, and where critical systems sit. Supports placement and access decisions.</t>
+          <t>Current list of individuals authorized to access each controlled area (dispatch floor, equipment room, server room, IT closet), with the key/badge issuance and deprovisioning record. Maintained per the Physical Access Control Policy.</t>
         </is>
       </c>
       <c r="L36" s="17" t="n"/>
@@ -2489,12 +2509,12 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>T2-07</t>
+          <t>T2-06</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>A-150</t>
+          <t>A-148</t>
         </is>
       </c>
       <c r="E37" s="15" t="n"/>
@@ -2505,17 +2525,17 @@
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>Physical Access Review Records</t>
+          <t>Controlled Area / Zone Map</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Architecture / Design</t>
         </is>
       </c>
       <c r="I37" s="17" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
@@ -2525,7 +2545,7 @@
       </c>
       <c r="K37" s="17" t="inlineStr">
         <is>
-          <t>Dated review of physical access events (badge swipes, door openings, failed attempts, equipment movement, badge incidents) for anomalies, fed into the security monitoring platform; who reviewed and what action followed.</t>
+          <t>Diagram of the facility's controlled areas and security zones, the access level for each, and where critical systems sit. Supports placement and access decisions.</t>
         </is>
       </c>
       <c r="L37" s="17" t="n"/>
@@ -2543,23 +2563,23 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>T2-08</t>
+          <t>T2-07</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>A-156</t>
+          <t>A-150</t>
         </is>
       </c>
       <c r="E38" s="15" t="n"/>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>A-155</t>
+          <t>A-069</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>Screening Completion Records</t>
+          <t>Physical Access Review Records</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
@@ -2569,7 +2589,7 @@
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>Confidential / CJIS</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
@@ -2579,7 +2599,7 @@
       </c>
       <c r="K38" s="17" t="inlineStr">
         <is>
-          <t>Dated evidence of completed background checks and clearance status by individual; access gated until vetting is logged.</t>
+          <t>Dated review of physical access events (badge swipes, door openings, failed attempts, equipment movement, badge incidents) for anomalies, fed into the security monitoring platform; who reviewed and what action followed.</t>
         </is>
       </c>
       <c r="L38" s="17" t="n"/>
@@ -2597,33 +2617,33 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>T2-09</t>
+          <t>T2-08</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>A-162</t>
+          <t>A-156</t>
         </is>
       </c>
       <c r="E39" s="15" t="n"/>
       <c r="F39" s="15" t="inlineStr">
         <is>
-          <t>A-086</t>
+          <t>A-155</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>Role-Specific Training Materials</t>
+          <t>Screening Completion Records</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>Training Material</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Confidential / CJIS</t>
         </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
@@ -2633,7 +2653,7 @@
       </c>
       <c r="K39" s="17" t="inlineStr">
         <is>
-          <t>Specialized training content by role (secure configuration, vulnerability management, incident response, data-classification handling), refreshed on a set schedule. Includes a secure media-handling module (secure transport and disposal) and physical/visual safeguards (screen lock, privacy filters, PII handling).</t>
+          <t>Dated evidence of completed background checks and clearance status by individual; access gated until vetting is logged.</t>
         </is>
       </c>
       <c r="L39" s="17" t="n"/>
@@ -2651,33 +2671,33 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>T2-10</t>
+          <t>T2-09</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>A-048</t>
+          <t>A-162</t>
         </is>
       </c>
       <c r="E40" s="15" t="n"/>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>A-047</t>
+          <t>A-086</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>External Connection Inventory</t>
+          <t>Role-Specific Training Materials</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Training Material</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J40" s="15" t="inlineStr">
@@ -2687,7 +2707,7 @@
       </c>
       <c r="K40" s="17" t="inlineStr">
         <is>
-          <t>Every external connection with business justification: ISP circuits, ESInet, cloud services, and vendor remote-access paths. Includes a trust-relationships section recording cross-system trusts and SAML federations. Reconciled on a set cadence.</t>
+          <t>Specialized training content by role (secure configuration, vulnerability management, incident response, data-classification handling), refreshed on a set schedule. Includes a secure media-handling module (secure transport and disposal) and physical/visual safeguards (screen lock, privacy filters, PII handling).</t>
         </is>
       </c>
       <c r="L40" s="17" t="n"/>
@@ -2705,19 +2725,23 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>T2-11</t>
+          <t>T2-10</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>A-079</t>
+          <t>A-048</t>
         </is>
       </c>
       <c r="E41" s="15" t="n"/>
-      <c r="F41" s="15" t="n"/>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>A-047</t>
+        </is>
+      </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>Vendor &amp; Contractor Inventory</t>
+          <t>External Connection Inventory</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
@@ -2737,7 +2761,7 @@
       </c>
       <c r="K41" s="17" t="inlineStr">
         <is>
-          <t>Single inventory of all externally managed systems, cloud services, and vendor relationships, with access scope and named technical/security contacts per vendor. Reconciled quarterly against active services.</t>
+          <t>Every external connection with business justification: ISP circuits, ESInet, cloud services, and vendor remote-access paths. Includes a trust-relationships section recording cross-system trusts and SAML federations. Reconciled on a set cadence.</t>
         </is>
       </c>
       <c r="L41" s="17" t="n"/>
@@ -2755,23 +2779,19 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>T2-12</t>
+          <t>T2-11</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>A-035</t>
+          <t>A-079</t>
         </is>
       </c>
       <c r="E42" s="15" t="n"/>
-      <c r="F42" s="15" t="inlineStr">
-        <is>
-          <t>A-010</t>
-        </is>
-      </c>
+      <c r="F42" s="15" t="n"/>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>Access Entitlement Matrix</t>
+          <t>Vendor &amp; Contractor Inventory</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
@@ -2781,7 +2801,7 @@
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>Restricted / CJIS</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J42" s="15" t="inlineStr">
@@ -2791,7 +2811,7 @@
       </c>
       <c r="K42" s="17" t="inlineStr">
         <is>
-          <t>Maps each staff role and vendor type to the systems and data they are authorized to access, with the access level for each. The role-to-system reference behind least-privilege reviews. Reconciled against active accounts on a set cadence.</t>
+          <t>Single inventory of all externally managed systems, cloud services, and vendor relationships, with access scope and named technical/security contacts per vendor. Reconciled quarterly against active services.</t>
         </is>
       </c>
       <c r="L42" s="17" t="n"/>
@@ -2809,33 +2829,33 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>T2-13</t>
+          <t>T2-12</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>A-011</t>
+          <t>A-035</t>
         </is>
       </c>
       <c r="E43" s="15" t="n"/>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>A-037</t>
+          <t>A-010</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
         <is>
-          <t>Account Provisioning &amp; Deprovisioning Checklist</t>
+          <t>Access Entitlement Matrix</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>Confidential / CJIS</t>
+          <t>Restricted / CJIS</t>
         </is>
       </c>
       <c r="J43" s="15" t="inlineStr">
@@ -2845,7 +2865,7 @@
       </c>
       <c r="K43" s="17" t="inlineStr">
         <is>
-          <t>Per-system list of account actions in two sections: provisioning (onboarding) and deprovisioning (offboarding), covering user, remote, guest, temporary, vendor, and service accounts. The operational tool the provisioning/deprovisioning procedure runs from.</t>
+          <t>Maps each staff role and vendor type to the systems and data they are authorized to access, with the access level for each. The role-to-system reference behind least-privilege reviews. Reconciled against active accounts on a set cadence.</t>
         </is>
       </c>
       <c r="L43" s="17" t="n"/>
@@ -2863,28 +2883,28 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>T2-14</t>
+          <t>T2-13</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>A-038</t>
+          <t>A-011</t>
         </is>
       </c>
       <c r="E44" s="15" t="n"/>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>A-010</t>
+          <t>A-037</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>Periodic Account Review / Certification Records</t>
+          <t>Account Provisioning &amp; Deprovisioning Checklist</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
@@ -2899,7 +2919,7 @@
       </c>
       <c r="K44" s="17" t="inlineStr">
         <is>
-          <t>Dated record of regular access reviews confirming active accounts match current personnel and roles: who reviewed, and what was changed or removed. Evidence behind least-privilege and role-change/departure adjustments.</t>
+          <t>Per-system list of account actions in two sections: provisioning (onboarding) and deprovisioning (offboarding), covering user, remote, guest, temporary, vendor, and service accounts. The operational tool the provisioning/deprovisioning procedure runs from.</t>
         </is>
       </c>
       <c r="L44" s="17" t="n"/>
@@ -2917,12 +2937,12 @@
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>T2-15</t>
+          <t>T2-14</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>A-039</t>
+          <t>A-038</t>
         </is>
       </c>
       <c r="E45" s="15" t="n"/>
@@ -2933,17 +2953,17 @@
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>Password &amp; Authentication Policy</t>
+          <t>Periodic Account Review / Certification Records</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I45" s="17" t="inlineStr">
         <is>
-          <t>Internal / CJIS</t>
+          <t>Confidential / CJIS</t>
         </is>
       </c>
       <c r="J45" s="15" t="inlineStr">
@@ -2953,7 +2973,7 @@
       </c>
       <c r="K45" s="17" t="inlineStr">
         <is>
-          <t>Sets credential rules for all account types: complexity, length, rotation, secure storage (hashing/vaulting), bans on weak/reused/shared passwords, password-manager use, and strong-authentication methods (tokens, certificates, MFA). Identity proofing before issuance and unique credentials per user. Exceptions process captures systems not yet compliant with a target date, recorded in the Risk / Finding Register.</t>
+          <t>Dated record of regular access reviews confirming active accounts match current personnel and roles: who reviewed, and what was changed or removed. Evidence behind least-privilege and role-change/departure adjustments.</t>
         </is>
       </c>
       <c r="L45" s="17" t="n"/>
@@ -2971,19 +2991,23 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>T2-16</t>
+          <t>T2-15</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>A-050</t>
+          <t>A-039</t>
         </is>
       </c>
       <c r="E46" s="15" t="n"/>
-      <c r="F46" s="15" t="n"/>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>A-010</t>
+        </is>
+      </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>Remote Access Policy</t>
+          <t>Password &amp; Authentication Policy</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
@@ -2993,7 +3017,7 @@
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal / CJIS</t>
         </is>
       </c>
       <c r="J46" s="15" t="inlineStr">
@@ -3003,7 +3027,7 @@
       </c>
       <c r="K46" s="17" t="inlineStr">
         <is>
-          <t>Who may connect remotely, from what device types, through what approved methods (VPN, virtual desktop, secure shell), and under what conditions (MFA, approved devices, time windows). Sets hardening expectations and the monitoring/logging of remote sessions. Addresses high-risk vendor remote access.</t>
+          <t>Sets credential rules for all account types: complexity, length, rotation, secure storage (hashing/vaulting), bans on weak/reused/shared passwords, password-manager use, and strong-authentication methods (tokens, certificates, MFA). Identity proofing before issuance and unique credentials per user. Exceptions process captures systems not yet compliant with a target date, recorded in the Risk / Finding Register.</t>
         </is>
       </c>
       <c r="L46" s="17" t="n"/>
@@ -3021,33 +3045,29 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>T2-17</t>
+          <t>T2-16</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>A-080</t>
+          <t>A-050</t>
         </is>
       </c>
       <c r="E47" s="15" t="n"/>
-      <c r="F47" s="15" t="inlineStr">
-        <is>
-          <t>A-079</t>
-        </is>
-      </c>
+      <c r="F47" s="15" t="n"/>
       <c r="G47" s="17" t="inlineStr">
         <is>
-          <t>Third-Party Access Agreement</t>
+          <t>Remote Access Policy</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>Agreement / Form</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
-          <t>Restricted / CJIS</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J47" s="15" t="inlineStr">
@@ -3057,7 +3077,7 @@
       </c>
       <c r="K47" s="17" t="inlineStr">
         <is>
-          <t>Signed agreement governing the terms, scope, and security obligations of each vendor relationship involving system or data access; retained per vendor.</t>
+          <t>Who may connect remotely, from what device types, through what approved methods (VPN, virtual desktop, secure shell), and under what conditions (MFA, approved devices, time windows). Sets hardening expectations and the monitoring/logging of remote sessions. Addresses high-risk vendor remote access.</t>
         </is>
       </c>
       <c r="L47" s="17" t="n"/>
@@ -3075,28 +3095,28 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>T2-18</t>
+          <t>T2-17</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>A-093</t>
+          <t>A-080</t>
         </is>
       </c>
       <c r="E48" s="15" t="n"/>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>A-010</t>
+          <t>A-079</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>Role-Based Access Control (RBAC) Documentation</t>
+          <t>Third-Party Access Agreement</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Agreement / Form</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
@@ -3111,7 +3131,7 @@
       </c>
       <c r="K48" s="17" t="inlineStr">
         <is>
-          <t>Documents role definitions and the permissions mapped to each role, enforcing least privilege across routine, temporary, privileged, and remote accounts. Includes a separation-of-duties pairing table (e.g., system administration vs audit) so no one both changes and reviews the same settings. Basis for periodic privilege reviews.</t>
+          <t>Signed agreement governing the terms, scope, and security obligations of each vendor relationship involving system or data access; retained per vendor.</t>
         </is>
       </c>
       <c r="L48" s="17" t="n"/>
@@ -3129,33 +3149,33 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>T2-19</t>
+          <t>T2-18</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>A-094</t>
+          <t>A-093</t>
         </is>
       </c>
       <c r="E49" s="15" t="n"/>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>A-093</t>
+          <t>A-010</t>
         </is>
       </c>
       <c r="G49" s="17" t="inlineStr">
         <is>
-          <t>Privilege Review Records</t>
+          <t>Role-Based Access Control (RBAC) Documentation</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
-          <t>Confidential / CJIS</t>
+          <t>Restricted / CJIS</t>
         </is>
       </c>
       <c r="J49" s="15" t="inlineStr">
@@ -3165,7 +3185,7 @@
       </c>
       <c r="K49" s="17" t="inlineStr">
         <is>
-          <t>Dated record of periodic least-privilege reviews against the RBAC definitions: what was reviewed, by whom, and what rights were confirmed or revoked.</t>
+          <t>Documents role definitions and the permissions mapped to each role, enforcing least privilege across routine, temporary, privileged, and remote accounts. Includes a separation-of-duties pairing table (e.g., system administration vs audit) so no one both changes and reviews the same settings. Basis for periodic privilege reviews.</t>
         </is>
       </c>
       <c r="L49" s="17" t="n"/>
@@ -3183,29 +3203,33 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>T2-20</t>
+          <t>T2-19</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>A-086</t>
+          <t>A-094</t>
         </is>
       </c>
       <c r="E50" s="15" t="n"/>
-      <c r="F50" s="15" t="n"/>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>A-093</t>
+        </is>
+      </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>Cybersecurity Training Plan</t>
+          <t>Privilege Review Records</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Confidential / CJIS</t>
         </is>
       </c>
       <c r="J50" s="15" t="inlineStr">
@@ -3215,7 +3239,7 @@
       </c>
       <c r="K50" s="17" t="inlineStr">
         <is>
-          <t>Annual training plan: content, delivery method, audience, frequency, and completion tracking, with role-based assignment (technical staff, dispatchers, administrative) against leadership-set targets. Topics include phishing, data handling, password hygiene, and incident reporting. Refreshed at least annually.</t>
+          <t>Dated record of periodic least-privilege reviews against the RBAC definitions: what was reviewed, by whom, and what rights were confirmed or revoked.</t>
         </is>
       </c>
       <c r="L50" s="17" t="n"/>
@@ -3233,33 +3257,29 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>T2-21</t>
+          <t>T2-20</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>A-025</t>
+          <t>A-086</t>
         </is>
       </c>
       <c r="E51" s="15" t="n"/>
-      <c r="F51" s="15" t="inlineStr">
-        <is>
-          <t>A-024</t>
-        </is>
-      </c>
+      <c r="F51" s="15" t="n"/>
       <c r="G51" s="17" t="inlineStr">
         <is>
-          <t>Signed Acknowledgment Records</t>
+          <t>Cybersecurity Training Plan</t>
         </is>
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>Agreement / Form</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="I51" s="17" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J51" s="15" t="inlineStr">
@@ -3269,7 +3289,7 @@
       </c>
       <c r="K51" s="17" t="inlineStr">
         <is>
-          <t>Individual record of each employee and contractor who has read and signed the AUP, renewed at least annually. Includes a media-handling acknowledgment variant for personnel who handle or transport sensitive media.</t>
+          <t>Annual training plan: content, delivery method, audience, frequency, and completion tracking, with role-based assignment (technical staff, dispatchers, administrative) against leadership-set targets. Topics include phishing, data handling, password hygiene, and incident reporting. Refreshed at least annually.</t>
         </is>
       </c>
       <c r="L51" s="17" t="n"/>
@@ -3287,28 +3307,28 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>T2-22</t>
+          <t>T2-21</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>A-088</t>
+          <t>A-025</t>
         </is>
       </c>
       <c r="E52" s="15" t="n"/>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>A-086</t>
+          <t>A-024</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>New Employee Training Checklist (Pre-Access)</t>
+          <t>Signed Acknowledgment Records</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Agreement / Form</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
@@ -3323,7 +3343,7 @@
       </c>
       <c r="K52" s="17" t="inlineStr">
         <is>
-          <t>Security training a new employee must complete before unsupervised access to PSAP systems, with sign-off; access gated until complete.</t>
+          <t>Individual record of each employee and contractor who has read and signed the AUP, renewed at least annually. Includes a media-handling acknowledgment variant for personnel who handle or transport sensitive media.</t>
         </is>
       </c>
       <c r="L52" s="17" t="n"/>
@@ -3341,33 +3361,33 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>T2-23</t>
+          <t>T2-22</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>A-089</t>
+          <t>A-088</t>
         </is>
       </c>
       <c r="E53" s="15" t="n"/>
       <c r="F53" s="15" t="inlineStr">
         <is>
-          <t>A-024</t>
+          <t>A-086</t>
         </is>
       </c>
       <c r="G53" s="17" t="inlineStr">
         <is>
-          <t>Social Media &amp; External Communications Policy</t>
+          <t>New Employee Training Checklist (Pre-Access)</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="J53" s="15" t="inlineStr">
@@ -3377,7 +3397,7 @@
       </c>
       <c r="K53" s="17" t="inlineStr">
         <is>
-          <t>Guidance on social-media use, personal/business crossover, personal-device use on the PSAP network, and handling of non-public information. Extends the AUP.</t>
+          <t>Security training a new employee must complete before unsupervised access to PSAP systems, with sign-off; access gated until complete.</t>
         </is>
       </c>
       <c r="L53" s="17" t="n"/>
@@ -3395,33 +3415,33 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>T2-24</t>
+          <t>T2-23</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>A-090</t>
+          <t>A-089</t>
         </is>
       </c>
       <c r="E54" s="15" t="n"/>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>A-025</t>
+          <t>A-024</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>Policy Acknowledgment Tracking Log</t>
+          <t>Social Media &amp; External Communications Policy</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J54" s="15" t="inlineStr">
@@ -3431,7 +3451,7 @@
       </c>
       <c r="K54" s="17" t="inlineStr">
         <is>
-          <t>Confirms all active staff have current acknowledgments on file (AUP and role-specific) and flags gaps. The tracking view behind the signed records.</t>
+          <t>Guidance on social-media use, personal/business crossover, personal-device use on the PSAP network, and handling of non-public information. Extends the AUP.</t>
         </is>
       </c>
       <c r="L54" s="17" t="n"/>
@@ -3449,33 +3469,33 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>T2-25</t>
+          <t>T2-24</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>A-074</t>
+          <t>A-090</t>
         </is>
       </c>
       <c r="E55" s="15" t="n"/>
       <c r="F55" s="15" t="inlineStr">
         <is>
-          <t>A-069</t>
+          <t>A-025</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
         <is>
-          <t>Physical Security Hardening Standard</t>
+          <t>Policy Acknowledgment Tracking Log</t>
         </is>
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="J55" s="15" t="inlineStr">
@@ -3485,7 +3505,7 @@
       </c>
       <c r="K55" s="17" t="inlineStr">
         <is>
-          <t>Hardening requirements for equipment areas: cable management and labeling, equipment locking, restricted-zone placement, and display protection (privacy filters, auto-lock) for dispatch terminals and call-taker screens. Includes equipment placement requirements (restricted, climate-controlled areas matching classification, with a placement review cadence). The governing requirements behind the hardening assessment.</t>
+          <t>Confirms all active staff have current acknowledgments on file (AUP and role-specific) and flags gaps. The tracking view behind the signed records.</t>
         </is>
       </c>
       <c r="L55" s="17" t="n"/>
@@ -3503,28 +3523,28 @@
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>T2-26</t>
+          <t>T2-25</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>A-165</t>
+          <t>A-074</t>
         </is>
       </c>
       <c r="E56" s="15" t="n"/>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>A-074</t>
+          <t>A-069</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>Server Room / Equipment Area Hardening Assessment Record</t>
+          <t>Physical Security Hardening Standard</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>Report / Assessment</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
@@ -3539,7 +3559,7 @@
       </c>
       <c r="K56" s="17" t="inlineStr">
         <is>
-          <t>As-built assessment of equipment-area hardening against the standard, noting gaps given facility constraints. Includes a shared-space risk section where PSAP equipment is co-located with other agency equipment, with compensating controls.</t>
+          <t>Hardening requirements for equipment areas: cable management and labeling, equipment locking, restricted-zone placement, and display protection (privacy filters, auto-lock) for dispatch terminals and call-taker screens. Includes equipment placement requirements (restricted, climate-controlled areas matching classification, with a placement review cadence). The governing requirements behind the hardening assessment.</t>
         </is>
       </c>
       <c r="L56" s="17" t="n"/>
@@ -3552,38 +3572,38 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>T3-01</t>
+          <t>T2-26</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>A-052</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="n"/>
+          <t>A-165</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="n"/>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>A-074</t>
+        </is>
+      </c>
       <c r="G57" s="17" t="inlineStr">
         <is>
-          <t>Change Management Policy</t>
+          <t>Server Room / Equipment Area Hardening Assessment Record</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Report / Assessment</t>
         </is>
       </c>
       <c r="I57" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J57" s="15" t="inlineStr">
@@ -3593,7 +3613,7 @@
       </c>
       <c r="K57" s="17" t="inlineStr">
         <is>
-          <t>Defines what constitutes a change, the approval workflow, documentation, and review of deviations, across every system. Adds three sections: DNS administration and change governance; Supervised Maintenance (authorized personnel, scheduled windows, pre-maintenance backups, second-person signoff); and a Security Assessment Gate for major deployments/changes (risk-scaled assessment including a cryptographic review, signoff before go-live). Foundational for all technical change records.</t>
+          <t>As-built assessment of equipment-area hardening against the standard, noting gaps given facility constraints. Includes a shared-space risk section where PSAP equipment is co-located with other agency equipment, with compensating controls.</t>
         </is>
       </c>
       <c r="L57" s="17" t="n"/>
@@ -3611,33 +3631,33 @@
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>T3-02</t>
+          <t>T3-01</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>A-104</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="n"/>
-      <c r="F58" s="15" t="inlineStr">
-        <is>
-          <t>A-047</t>
-        </is>
-      </c>
+          <t>A-052</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="n"/>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>Network Segmentation Design Document</t>
+          <t>Change Management Policy</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>Architecture / Design</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J58" s="15" t="inlineStr">
@@ -3647,7 +3667,7 @@
       </c>
       <c r="K58" s="17" t="inlineStr">
         <is>
-          <t>The segmentation model: VLANs and physical partitions, ACLs and inter-segment rules, DMZs, micro-segmentation, and isolation of critical services (GIS, call routing) from general-use systems. The design behind the firewall ruleset.</t>
+          <t>Defines what constitutes a change, the approval workflow, documentation, and review of deviations, across every system. Adds three sections: DNS administration and change governance; Supervised Maintenance (authorized personnel, scheduled windows, pre-maintenance backups, second-person signoff); and a Security Assessment Gate for major deployments/changes (risk-scaled assessment including a cryptographic review, signoff before go-live). Foundational for all technical change records.</t>
         </is>
       </c>
       <c r="L58" s="17" t="n"/>
@@ -3665,28 +3685,28 @@
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>T3-03</t>
+          <t>T3-02</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>A-118</t>
+          <t>A-104</t>
         </is>
       </c>
       <c r="E59" s="15" t="n"/>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>A-117</t>
+          <t>A-047</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr">
         <is>
-          <t>Configuration Drift Detection Records</t>
+          <t>Network Segmentation Design Document</t>
         </is>
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Architecture / Design</t>
         </is>
       </c>
       <c r="I59" s="17" t="inlineStr">
@@ -3701,7 +3721,7 @@
       </c>
       <c r="K59" s="17" t="inlineStr">
         <is>
-          <t>Automated comparison of current configuration against the baselines, with detected deviations, triage, and remediation. The evidence side of the System Configuration Baselines.</t>
+          <t>The segmentation model: VLANs and physical partitions, ACLs and inter-segment rules, DMZs, micro-segmentation, and isolation of critical services (GIS, call routing) from general-use systems. The design behind the firewall ruleset.</t>
         </is>
       </c>
       <c r="L59" s="17" t="n"/>
@@ -3719,24 +3739,28 @@
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>T3-04</t>
+          <t>T3-03</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>A-120</t>
+          <t>A-118</t>
         </is>
       </c>
       <c r="E60" s="15" t="n"/>
-      <c r="F60" s="15" t="n"/>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>A-117</t>
+        </is>
+      </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>Endpoint Security Software Inventory</t>
+          <t>Configuration Drift Detection Records</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
@@ -3751,7 +3775,7 @@
       </c>
       <c r="K60" s="17" t="inlineStr">
         <is>
-          <t>Anti-malware, host firewall, and EDR tools deployed across the endpoint population, with version and update status. Confirms layered endpoint protection on all critical systems.</t>
+          <t>Automated comparison of current configuration against the baselines, with detected deviations, triage, and remediation. The evidence side of the System Configuration Baselines.</t>
         </is>
       </c>
       <c r="L60" s="17" t="n"/>
@@ -3769,28 +3793,24 @@
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>T3-05</t>
+          <t>T3-04</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>A-119</t>
+          <t>A-120</t>
         </is>
       </c>
       <c r="E61" s="15" t="n"/>
-      <c r="F61" s="15" t="inlineStr">
-        <is>
-          <t>A-117</t>
-        </is>
-      </c>
+      <c r="F61" s="15" t="n"/>
       <c r="G61" s="17" t="inlineStr">
         <is>
-          <t>Endpoint Hardening Checklist</t>
+          <t>Endpoint Security Software Inventory</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I61" s="17" t="inlineStr">
@@ -3805,7 +3825,7 @@
       </c>
       <c r="K61" s="17" t="inlineStr">
         <is>
-          <t>Verifies each endpoint meets the secure baseline: disabled unnecessary services/ports/protocols, screen-lock timeouts, anti-malware present. Includes an email-server hardening section (DKIM/SPF/DMARC/TLS checks) and a VoIP/multimedia-server hardening section. Applied to new and existing devices.</t>
+          <t>Anti-malware, host firewall, and EDR tools deployed across the endpoint population, with version and update status. Confirms layered endpoint protection on all critical systems.</t>
         </is>
       </c>
       <c r="L61" s="17" t="n"/>
@@ -3823,37 +3843,33 @@
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>T3-06</t>
+          <t>T3-05</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>A-056</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>A-119</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="n"/>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>A-012</t>
+          <t>A-117</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>Encryption Policy</t>
+          <t>Endpoint Hardening Checklist</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J62" s="15" t="inlineStr">
@@ -3863,7 +3879,7 @@
       </c>
       <c r="K62" s="17" t="inlineStr">
         <is>
-          <t>Governing policy: which data categories require encryption at rest and in transit, tied to the data classification scheme, and the lifecycle expectations for cryptographic protection across public-safety systems. The Encryption Standards Document specifies the approved algorithms; verification records evidence compliance.</t>
+          <t>Verifies each endpoint meets the secure baseline: disabled unnecessary services/ports/protocols, screen-lock timeouts, anti-malware present. Includes an email-server hardening section (DKIM/SPF/DMARC/TLS checks) and a VoIP/multimedia-server hardening section. Applied to new and existing devices.</t>
         </is>
       </c>
       <c r="L62" s="17" t="n"/>
@@ -3881,33 +3897,37 @@
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>T3-07</t>
+          <t>T3-06</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>A-100</t>
-        </is>
-      </c>
-      <c r="E63" s="15" t="n"/>
+          <t>A-056</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>A-056</t>
+          <t>A-012</t>
         </is>
       </c>
       <c r="G63" s="17" t="inlineStr">
         <is>
-          <t>Encryption Standards Document</t>
+          <t>Encryption Policy</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J63" s="15" t="inlineStr">
@@ -3917,7 +3937,7 @@
       </c>
       <c r="K63" s="17" t="inlineStr">
         <is>
-          <t>Defines which data categories require encryption at rest and in transit, tied to the classification scheme, and the approved and prohibited cryptographic algorithm list (e.g., AES-256, TLS 1.2+; prohibit DES, RC4, TLS 1.0/1.1). The governing requirements the Encryption Policy and verification records implement.</t>
+          <t>Governing policy: which data categories require encryption at rest and in transit, tied to the data classification scheme, and the lifecycle expectations for cryptographic protection across public-safety systems. The Encryption Standards Document specifies the approved algorithms; verification records evidence compliance.</t>
         </is>
       </c>
       <c r="L63" s="17" t="n"/>
@@ -3935,28 +3955,28 @@
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>T3-08</t>
+          <t>T3-07</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>A-126</t>
+          <t>A-100</t>
         </is>
       </c>
       <c r="E64" s="15" t="n"/>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>A-100</t>
+          <t>A-056</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>Encryption Implementation Verification Records</t>
+          <t>Encryption Standards Document</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
@@ -3971,7 +3991,7 @@
       </c>
       <c r="K64" s="17" t="inlineStr">
         <is>
-          <t>As-built evidence that encryption is applied where required: system or data category, mechanism in use, validation/testing performed, and any exception with remediation date. The evidence side of the Encryption Standards Document.</t>
+          <t>Defines which data categories require encryption at rest and in transit, tied to the classification scheme, and the approved and prohibited cryptographic algorithm list (e.g., AES-256, TLS 1.2+; prohibit DES, RC4, TLS 1.0/1.1). The governing requirements the Encryption Policy and verification records implement.</t>
         </is>
       </c>
       <c r="L64" s="17" t="n"/>
@@ -3989,33 +4009,33 @@
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>T3-09</t>
+          <t>T3-08</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>A-129</t>
+          <t>A-126</t>
         </is>
       </c>
       <c r="E65" s="15" t="n"/>
       <c r="F65" s="15" t="inlineStr">
         <is>
-          <t>A-056</t>
+          <t>A-100</t>
         </is>
       </c>
       <c r="G65" s="17" t="inlineStr">
         <is>
-          <t>Key &amp; Certificate Management Policy</t>
+          <t>Encryption Implementation Verification Records</t>
         </is>
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J65" s="15" t="inlineStr">
@@ -4025,7 +4045,7 @@
       </c>
       <c r="K65" s="17" t="inlineStr">
         <is>
-          <t>Governs the cryptographic key lifecycle (generation, distribution, rotation, revocation, storage, escrow) and certificate management (request, approval, self-signed limits, expiration tracking). Sets separation of duties and approved key/certificate handling across public-safety systems. The key inventory, rotation schedule, escrow procedure, and certificate procedures implement it.</t>
+          <t>As-built evidence that encryption is applied where required: system or data category, mechanism in use, validation/testing performed, and any exception with remediation date. The evidence side of the Encryption Standards Document.</t>
         </is>
       </c>
       <c r="L65" s="17" t="n"/>
@@ -4043,33 +4063,33 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>T3-10</t>
+          <t>T3-09</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>A-020</t>
+          <t>A-129</t>
         </is>
       </c>
       <c r="E66" s="15" t="n"/>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>A-019</t>
+          <t>A-056</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>RTO/RPO Documentation</t>
+          <t>Key &amp; Certificate Management Policy</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>Reference Matrix</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J66" s="15" t="inlineStr">
@@ -4079,7 +4099,7 @@
       </c>
       <c r="K66" s="17" t="inlineStr">
         <is>
-          <t>System-by-system recovery time and recovery point objectives and the recovery sequence, derived from the criticality ranking. Defines the targets that recovery testing verifies.</t>
+          <t>Governs the cryptographic key lifecycle (generation, distribution, rotation, revocation, storage, escrow) and certificate management (request, approval, self-signed limits, expiration tracking). Sets separation of duties and approved key/certificate handling across public-safety systems. The key inventory, rotation schedule, escrow procedure, and certificate procedures implement it.</t>
         </is>
       </c>
       <c r="L66" s="17" t="n"/>
@@ -4097,33 +4117,33 @@
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>T3-11</t>
+          <t>T3-10</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>A-022</t>
+          <t>A-020</t>
         </is>
       </c>
       <c r="E67" s="15" t="n"/>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>A-003</t>
+          <t>A-019</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr">
         <is>
-          <t>Backup Policy</t>
+          <t>RTO/RPO Documentation</t>
         </is>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Reference Matrix</t>
         </is>
       </c>
       <c r="I67" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J67" s="15" t="inlineStr">
@@ -4133,7 +4153,7 @@
       </c>
       <c r="K67" s="17" t="inlineStr">
         <is>
-          <t>What is backed up, frequency, retention, encryption of backup media, immutability, and off-site/off-system storage, with a named owner, for all critical data (call recordings, dispatch logs, databases). Scope set by the asset inventory. Reviewed annually.</t>
+          <t>System-by-system recovery time and recovery point objectives and the recovery sequence, derived from the criticality ranking. Defines the targets that recovery testing verifies.</t>
         </is>
       </c>
       <c r="L67" s="17" t="n"/>
@@ -4151,33 +4171,33 @@
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>T3-12</t>
+          <t>T3-11</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>A-066</t>
+          <t>A-022</t>
         </is>
       </c>
       <c r="E68" s="15" t="n"/>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>A-022</t>
+          <t>A-003</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>Backup Schedule &amp; Media Inventory</t>
+          <t>Backup Policy</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J68" s="15" t="inlineStr">
@@ -4187,7 +4207,7 @@
       </c>
       <c r="K68" s="17" t="inlineStr">
         <is>
-          <t>How backup jobs are configured and that the schedule matches the policy, plus the inventory of backup media and where copies are stored. Operationalizes the Backup Policy.</t>
+          <t>What is backed up, frequency, retention, encryption of backup media, immutability, and off-site/off-system storage, with a named owner, for all critical data (call recordings, dispatch logs, databases). Scope set by the asset inventory. Reviewed annually.</t>
         </is>
       </c>
       <c r="L68" s="17" t="n"/>
@@ -4205,12 +4225,12 @@
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>T3-13</t>
+          <t>T3-12</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>A-067</t>
+          <t>A-066</t>
         </is>
       </c>
       <c r="E69" s="15" t="n"/>
@@ -4221,12 +4241,12 @@
       </c>
       <c r="G69" s="17" t="inlineStr">
         <is>
-          <t>Restoration Test Records</t>
+          <t>Backup Schedule &amp; Media Inventory</t>
         </is>
       </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="I69" s="17" t="inlineStr">
@@ -4241,7 +4261,7 @@
       </c>
       <c r="K69" s="17" t="inlineStr">
         <is>
-          <t>Dated evidence of restoration tests confirming data integrity and operational readiness, not just job completion: systems restored, results, and lessons. Verifies RTO/RPO are met.</t>
+          <t>How backup jobs are configured and that the schedule matches the policy, plus the inventory of backup media and where copies are stored. Operationalizes the Backup Policy.</t>
         </is>
       </c>
       <c r="L69" s="17" t="n"/>
@@ -4259,32 +4279,28 @@
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>T3-14</t>
+          <t>T3-13</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>A-017</t>
-        </is>
-      </c>
-      <c r="E70" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>A-067</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="n"/>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>A-014</t>
+          <t>A-022</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>Backup Call-Handling / Dispatch Continuity Procedure</t>
+          <t>Restoration Test Records</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
@@ -4299,7 +4315,7 @@
       </c>
       <c r="K70" s="17" t="inlineStr">
         <is>
-          <t>The operational protocol for continuing to receive and dispatch 9-1-1 calls when CAD or the primary call-handling system is unavailable: fallback steps, roles, and triggers. The most PSAP-specific artifact; built with the IRP and referenced by the COOP and TDoS procedure.</t>
+          <t>Dated evidence of restoration tests confirming data integrity and operational readiness, not just job completion: systems restored, results, and lessons. Verifies RTO/RPO are met.</t>
         </is>
       </c>
       <c r="L70" s="17" t="n"/>
@@ -4317,15 +4333,19 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>T3-15</t>
+          <t>T3-14</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>A-015</t>
-        </is>
-      </c>
-      <c r="E71" s="15" t="n"/>
+          <t>A-017</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
           <t>A-014</t>
@@ -4333,17 +4353,17 @@
       </c>
       <c r="G71" s="17" t="inlineStr">
         <is>
-          <t>Incident Classification &amp; Severity Matrix</t>
+          <t>Backup Call-Handling / Dispatch Continuity Procedure</t>
         </is>
       </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>Reference Matrix</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
-          <t>Restricted / CJIS</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J71" s="15" t="inlineStr">
@@ -4353,7 +4373,7 @@
       </c>
       <c r="K71" s="17" t="inlineStr">
         <is>
-          <t>Severity tiers with examples and the response protocol each tier triggers. Companion to the IRP and the basis for notification timing and escalation.</t>
+          <t>The operational protocol for continuing to receive and dispatch 9-1-1 calls when CAD or the primary call-handling system is unavailable: fallback steps, roles, and triggers. The most PSAP-specific artifact; built with the IRP and referenced by the COOP and TDoS procedure.</t>
         </is>
       </c>
       <c r="L71" s="17" t="n"/>
@@ -4371,12 +4391,12 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>T3-16</t>
+          <t>T3-15</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>A-016</t>
+          <t>A-015</t>
         </is>
       </c>
       <c r="E72" s="15" t="n"/>
@@ -4387,17 +4407,17 @@
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>Incident Notification &amp; Escalation Contact List</t>
+          <t>Incident Classification &amp; Severity Matrix</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Reference Matrix</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>Confidential / CJIS</t>
+          <t>Restricted / CJIS</t>
         </is>
       </c>
       <c r="J72" s="15" t="inlineStr">
@@ -4407,7 +4427,7 @@
       </c>
       <c r="K72" s="17" t="inlineStr">
         <is>
-          <t>Who is called, in what order, per incident tier: internal contacts, vendors (CAD, recording, ISP), state 911 board, IOT, FBI/CISA, and any managed security service. Updated at least annually; maintained separately from the IRP for operational ease.</t>
+          <t>Severity tiers with examples and the response protocol each tier triggers. Companion to the IRP and the basis for notification timing and escalation.</t>
         </is>
       </c>
       <c r="L72" s="17" t="n"/>
@@ -4425,12 +4445,12 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>T3-17</t>
+          <t>T3-16</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>A-018</t>
+          <t>A-016</t>
         </is>
       </c>
       <c r="E73" s="15" t="n"/>
@@ -4441,17 +4461,17 @@
       </c>
       <c r="G73" s="17" t="inlineStr">
         <is>
-          <t>Tabletop Exercise Records</t>
+          <t>Incident Notification &amp; Escalation Contact List</t>
         </is>
       </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I73" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Confidential / CJIS</t>
         </is>
       </c>
       <c r="J73" s="15" t="inlineStr">
@@ -4461,7 +4481,7 @@
       </c>
       <c r="K73" s="17" t="inlineStr">
         <is>
-          <t>Record of each tabletop exercise: scenario, participants, facilitator, date, and observations. Used after the IRP exists; feeds the after-action reports and IRP revisions.</t>
+          <t>Who is called, in what order, per incident tier: internal contacts, vendors (CAD, recording, ISP), state 911 board, IOT, FBI/CISA, and any managed security service. Updated at least annually; maintained separately from the IRP for operational ease.</t>
         </is>
       </c>
       <c r="L73" s="17" t="n"/>
@@ -4479,23 +4499,23 @@
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>T3-18</t>
+          <t>T3-17</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>A-087</t>
+          <t>A-018</t>
         </is>
       </c>
       <c r="E74" s="15" t="n"/>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>A-086</t>
+          <t>A-014</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>Training Completion Records</t>
+          <t>Tabletop Exercise Records</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
@@ -4505,7 +4525,7 @@
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
-          <t>Confidential / CJIS</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J74" s="15" t="inlineStr">
@@ -4515,7 +4535,7 @@
       </c>
       <c r="K74" s="17" t="inlineStr">
         <is>
-          <t>Single completion log with a role/course field covering both general and role-based training: who completed what and when, current and prior year retained, reported to leadership. CJIS completion tracked separately in its dedicated record.</t>
+          <t>Record of each tabletop exercise: scenario, participants, facilitator, date, and observations. Used after the IRP exists; feeds the after-action reports and IRP revisions.</t>
         </is>
       </c>
       <c r="L74" s="17" t="n"/>
@@ -4533,33 +4553,33 @@
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>T3-19</t>
+          <t>T3-18</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>A-019</t>
-        </is>
-      </c>
-      <c r="E75" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F75" s="15" t="n"/>
+          <t>A-087</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="n"/>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>A-086</t>
+        </is>
+      </c>
       <c r="G75" s="17" t="inlineStr">
         <is>
-          <t>Continuity of Operations Plan (COOP)</t>
+          <t>Training Completion Records</t>
         </is>
       </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I75" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Confidential / CJIS</t>
         </is>
       </c>
       <c r="J75" s="15" t="inlineStr">
@@ -4569,7 +4589,7 @@
       </c>
       <c r="K75" s="17" t="inlineStr">
         <is>
-          <t>Contingency plan for 9-1-1-specific disruptions (call-routing failure, CAD outage, full facility loss, cyberattack, natural disaster, power failure): roles and responsibilities, activation triggers, overflow-routing protocol, alternate sites, and degraded-mode compensating controls. Built from the asset criticality ranking; reviewed annually.</t>
+          <t>Single completion log with a role/course field covering both general and role-based training: who completed what and when, current and prior year retained, reported to leadership. CJIS completion tracked separately in its dedicated record.</t>
         </is>
       </c>
       <c r="L75" s="17" t="n"/>
@@ -4587,28 +4607,28 @@
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>T3-20</t>
+          <t>T3-19</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>A-021</t>
-        </is>
-      </c>
-      <c r="E76" s="15" t="n"/>
-      <c r="F76" s="15" t="inlineStr">
-        <is>
           <t>A-019</t>
         </is>
       </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F76" s="15" t="n"/>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>Overflow Routing Agreement (Mutual Aid)</t>
+          <t>Continuity of Operations Plan (COOP)</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>Agreement / Form</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="I76" s="17" t="inlineStr">
@@ -4623,7 +4643,7 @@
       </c>
       <c r="K76" s="17" t="inlineStr">
         <is>
-          <t>Documented mutual-aid or overflow arrangement with one or more neighboring PSAPs: scope, triggers, and contacts. Reviewed and reconfirmed at least annually; pairs with the COOP.</t>
+          <t>Contingency plan for 9-1-1-specific disruptions (call-routing failure, CAD outage, full facility loss, cyberattack, natural disaster, power failure): roles and responsibilities, activation triggers, overflow-routing protocol, alternate sites, and degraded-mode compensating controls. Built from the asset criticality ranking; reviewed annually.</t>
         </is>
       </c>
       <c r="L76" s="17" t="n"/>
@@ -4641,12 +4661,12 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>T3-21</t>
+          <t>T3-20</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>A-065</t>
+          <t>A-021</t>
         </is>
       </c>
       <c r="E77" s="15" t="n"/>
@@ -4657,12 +4677,12 @@
       </c>
       <c r="G77" s="17" t="inlineStr">
         <is>
-          <t>Continuity Plan Exercise Records</t>
+          <t>Overflow Routing Agreement (Mutual Aid)</t>
         </is>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Agreement / Form</t>
         </is>
       </c>
       <c r="I77" s="17" t="inlineStr">
@@ -4677,7 +4697,7 @@
       </c>
       <c r="K77" s="17" t="inlineStr">
         <is>
-          <t>Dated evidence the COOP has been tested (tabletop at minimum): scenario, participants, results, and lessons feeding plan revisions.</t>
+          <t>Documented mutual-aid or overflow arrangement with one or more neighboring PSAPs: scope, triggers, and contacts. Reviewed and reconfirmed at least annually; pairs with the COOP.</t>
         </is>
       </c>
       <c r="L77" s="17" t="n"/>
@@ -4695,12 +4715,12 @@
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>T3-22</t>
+          <t>T3-21</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>A-143</t>
+          <t>A-065</t>
         </is>
       </c>
       <c r="E78" s="15" t="n"/>
@@ -4711,12 +4731,12 @@
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>System Redundancy Design Documentation</t>
+          <t>Continuity Plan Exercise Records</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>Architecture / Design</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I78" s="17" t="inlineStr">
@@ -4731,7 +4751,7 @@
       </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
-          <t>All redundant components (dual ISP, redundant CAD/call-routing, geographic and vendor diversity) and the failover mechanism for each, so a localized failure or vendor outage does not take down all services.</t>
+          <t>Dated evidence the COOP has been tested (tabletop at minimum): scenario, participants, results, and lessons feeding plan revisions.</t>
         </is>
       </c>
       <c r="L78" s="17" t="n"/>
@@ -4749,28 +4769,28 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>T3-23</t>
+          <t>T3-22</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>A-144</t>
+          <t>A-143</t>
         </is>
       </c>
       <c r="E79" s="15" t="n"/>
       <c r="F79" s="15" t="inlineStr">
         <is>
-          <t>A-143</t>
+          <t>A-019</t>
         </is>
       </c>
       <c r="G79" s="17" t="inlineStr">
         <is>
-          <t>Failover Test Records</t>
+          <t>System Redundancy Design Documentation</t>
         </is>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Architecture / Design</t>
         </is>
       </c>
       <c r="I79" s="17" t="inlineStr">
@@ -4785,7 +4805,7 @@
       </c>
       <c r="K79" s="17" t="inlineStr">
         <is>
-          <t>Documented tests of each failover path under simulated failure: scenario, result, time to shift, and remediation. Evidence behind the redundancy design.</t>
+          <t>All redundant components (dual ISP, redundant CAD/call-routing, geographic and vendor diversity) and the failover mechanism for each, so a localized failure or vendor outage does not take down all services.</t>
         </is>
       </c>
       <c r="L79" s="17" t="n"/>
@@ -4803,33 +4823,33 @@
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>T3-24</t>
+          <t>T3-23</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>A-058</t>
+          <t>A-144</t>
         </is>
       </c>
       <c r="E80" s="15" t="n"/>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>A-057</t>
+          <t>A-143</t>
         </is>
       </c>
       <c r="G80" s="17" t="inlineStr">
         <is>
-          <t>Log Retention Schedule</t>
+          <t>Failover Test Records</t>
         </is>
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J80" s="15" t="inlineStr">
@@ -4839,7 +4859,7 @@
       </c>
       <c r="K80" s="17" t="inlineStr">
         <is>
-          <t>Retention period per log source against operational, legal, and regulatory requirements, online versus archived, and where archived logs are retrieved. Implements the Logging Policy.</t>
+          <t>Documented tests of each failover path under simulated failure: scenario, result, time to shift, and remediation. Evidence behind the redundancy design.</t>
         </is>
       </c>
       <c r="L80" s="17" t="n"/>
@@ -4857,29 +4877,33 @@
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>T3-25</t>
+          <t>T3-24</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>A-081</t>
+          <t>A-058</t>
         </is>
       </c>
       <c r="E81" s="15" t="n"/>
-      <c r="F81" s="15" t="n"/>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>A-057</t>
+        </is>
+      </c>
       <c r="G81" s="17" t="inlineStr">
         <is>
-          <t>Vulnerability Assessment Reports</t>
+          <t>Log Retention Schedule</t>
         </is>
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>Report / Assessment</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="I81" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J81" s="15" t="inlineStr">
@@ -4889,7 +4913,7 @@
       </c>
       <c r="K81" s="17" t="inlineStr">
         <is>
-          <t>Scan and assessment findings across software, hardware, and network: scope, tool, findings, and risk rating, feeding the remediation register. Penetration tests are treated as a form of this report, with system owners and an independent assessor reviewing scope, methods, and findings.</t>
+          <t>Retention period per log source against operational, legal, and regulatory requirements, online versus archived, and where archived logs are retrieved. Implements the Logging Policy.</t>
         </is>
       </c>
       <c r="L81" s="17" t="n"/>
@@ -4907,24 +4931,24 @@
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>T3-26</t>
+          <t>T3-25</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>A-160</t>
+          <t>A-081</t>
         </is>
       </c>
       <c r="E82" s="15" t="n"/>
       <c r="F82" s="15" t="n"/>
       <c r="G82" s="17" t="inlineStr">
         <is>
-          <t>Vulnerability Scanning Schedule</t>
+          <t>Vulnerability Assessment Reports</t>
         </is>
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Report / Assessment</t>
         </is>
       </c>
       <c r="I82" s="17" t="inlineStr">
@@ -4939,7 +4963,7 @@
       </c>
       <c r="K82" s="17" t="inlineStr">
         <is>
-          <t>Scan frequency, scope, and tool, plus the penetration-test and independent-assessment cadence. Lists item, frequency, last run, next due, owner.</t>
+          <t>Scan and assessment findings across software, hardware, and network: scope, tool, findings, and risk rating, feeding the remediation register. Penetration tests are treated as a form of this report, with system owners and an independent assessor reviewing scope, methods, and findings.</t>
         </is>
       </c>
       <c r="L82" s="17" t="n"/>
@@ -4957,33 +4981,29 @@
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>T3-27</t>
+          <t>T3-26</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>A-013</t>
+          <t>A-160</t>
         </is>
       </c>
       <c r="E83" s="15" t="n"/>
-      <c r="F83" s="15" t="inlineStr">
-        <is>
-          <t>A-012</t>
-        </is>
-      </c>
+      <c r="F83" s="15" t="n"/>
       <c r="G83" s="17" t="inlineStr">
         <is>
-          <t>CJIS Data Handling Addendum</t>
+          <t>Vulnerability Scanning Schedule</t>
         </is>
       </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="I83" s="17" t="inlineStr">
         <is>
-          <t>Internal / CJIS</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J83" s="15" t="inlineStr">
@@ -4993,7 +5013,7 @@
       </c>
       <c r="K83" s="17" t="inlineStr">
         <is>
-          <t>Documents how CJIS-regulated data (reached via IDACS in Indiana) sits within the classification scheme and the additional CJIS Security Policy handling that applies on top of the base classification. References, does not restate, the CJIS policy; cites CJIS and 240 IAC 5 together where IDACS is in scope.</t>
+          <t>Scan frequency, scope, and tool, plus the penetration-test and independent-assessment cadence. Lists item, frequency, last run, next due, owner.</t>
         </is>
       </c>
       <c r="L83" s="17" t="n"/>
@@ -5011,29 +5031,33 @@
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>T3-28</t>
+          <t>T3-27</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>A-078</t>
+          <t>A-013</t>
         </is>
       </c>
       <c r="E84" s="15" t="n"/>
-      <c r="F84" s="15" t="n"/>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>A-012</t>
+        </is>
+      </c>
       <c r="G84" s="17" t="inlineStr">
         <is>
-          <t>Vendor Security Assessment Questionnaire</t>
+          <t>CJIS Data Handling Addendum</t>
         </is>
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal / CJIS</t>
         </is>
       </c>
       <c r="J84" s="15" t="inlineStr">
@@ -5043,7 +5067,7 @@
       </c>
       <c r="K84" s="17" t="inlineStr">
         <is>
-          <t>Standardized questionnaire to evaluate the security posture of new and existing vendors with significant system or data access; feeds the third-party risk records.</t>
+          <t>Documents how CJIS-regulated data (reached via IDACS in Indiana) sits within the classification scheme and the additional CJIS Security Policy handling that applies on top of the base classification. References, does not restate, the CJIS policy; cites CJIS and 240 IAC 5 together where IDACS is in scope.</t>
         </is>
       </c>
       <c r="L84" s="17" t="n"/>
@@ -5061,29 +5085,29 @@
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>T3-29</t>
+          <t>T3-28</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>A-076</t>
+          <t>A-078</t>
         </is>
       </c>
       <c r="E85" s="15" t="n"/>
       <c r="F85" s="15" t="n"/>
       <c r="G85" s="17" t="inlineStr">
         <is>
-          <t>Third-Party Risk Assessment Records</t>
+          <t>Vendor Security Assessment Questionnaire</t>
         </is>
       </c>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>Report / Assessment</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J85" s="15" t="inlineStr">
@@ -5093,7 +5117,7 @@
       </c>
       <c r="K85" s="17" t="inlineStr">
         <is>
-          <t>Completed vendor security assessments and ongoing monitoring for hosted/managed providers (CAD, GIS, VoIP, cloud storage): findings, risk rating, mitigations, and remediation commitments. Continuous monitoring method noted.</t>
+          <t>Standardized questionnaire to evaluate the security posture of new and existing vendors with significant system or data access; feeds the third-party risk records.</t>
         </is>
       </c>
       <c r="L85" s="17" t="n"/>
@@ -5111,29 +5135,29 @@
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>T3-30</t>
+          <t>T3-29</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>A-077</t>
+          <t>A-076</t>
         </is>
       </c>
       <c r="E86" s="15" t="n"/>
       <c r="F86" s="15" t="n"/>
       <c r="G86" s="17" t="inlineStr">
         <is>
-          <t>Security Requirements in Vendor Contracts / SLAs</t>
+          <t>Third-Party Risk Assessment Records</t>
         </is>
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>Agreement / Form</t>
+          <t>Report / Assessment</t>
         </is>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J86" s="15" t="inlineStr">
@@ -5143,7 +5167,7 @@
       </c>
       <c r="K86" s="17" t="inlineStr">
         <is>
-          <t>Clause templates for vendor contracts: data-protection standards, inventory accuracy, change notification, breach reporting, audit rights, and SLAs. Referenced when contracting hosted or managed services. CJIS data-handling addendum applies where in scope.</t>
+          <t>Completed vendor security assessments and ongoing monitoring for hosted/managed providers (CAD, GIS, VoIP, cloud storage): findings, risk rating, mitigations, and remediation commitments. Continuous monitoring method noted.</t>
         </is>
       </c>
       <c r="L86" s="17" t="n"/>
@@ -5161,33 +5185,29 @@
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>T3-31</t>
+          <t>T3-30</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>A-161</t>
+          <t>A-077</t>
         </is>
       </c>
       <c r="E87" s="15" t="n"/>
-      <c r="F87" s="15" t="inlineStr">
-        <is>
-          <t>A-086</t>
-        </is>
-      </c>
+      <c r="F87" s="15" t="n"/>
       <c r="G87" s="17" t="inlineStr">
         <is>
-          <t>Phishing Simulation Results</t>
+          <t>Security Requirements in Vendor Contracts / SLAs</t>
         </is>
       </c>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Agreement / Form</t>
         </is>
       </c>
       <c r="I87" s="17" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J87" s="15" t="inlineStr">
@@ -5197,7 +5217,7 @@
       </c>
       <c r="K87" s="17" t="inlineStr">
         <is>
-          <t>Results of phishing simulations: campaign, click and report rates, and follow-up, feeding training updates and awareness metrics.</t>
+          <t>Clause templates for vendor contracts: data-protection standards, inventory accuracy, change notification, breach reporting, audit rights, and SLAs. Referenced when contracting hosted or managed services. CJIS data-handling addendum applies where in scope.</t>
         </is>
       </c>
       <c r="L87" s="17" t="n"/>
@@ -5215,23 +5235,23 @@
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>T3-32</t>
+          <t>T3-31</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>A-164</t>
+          <t>A-161</t>
         </is>
       </c>
       <c r="E88" s="15" t="n"/>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>A-162</t>
+          <t>A-086</t>
         </is>
       </c>
       <c r="G88" s="17" t="inlineStr">
         <is>
-          <t>Competency Assessment Records</t>
+          <t>Phishing Simulation Results</t>
         </is>
       </c>
       <c r="H88" s="17" t="inlineStr">
@@ -5241,7 +5261,7 @@
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
-          <t>Confidential / CJIS</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="J88" s="15" t="inlineStr">
@@ -5251,7 +5271,7 @@
       </c>
       <c r="K88" s="17" t="inlineStr">
         <is>
-          <t>Records that staff in technical and security-sensitive roles demonstrate competency, not just attendance: assessment, result, and any remediation. Supports certification and continuing-education tracking.</t>
+          <t>Results of phishing simulations: campaign, click and report rates, and follow-up, feeding training updates and awareness metrics.</t>
         </is>
       </c>
       <c r="L88" s="17" t="n"/>
@@ -5269,33 +5289,33 @@
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>T3-33</t>
+          <t>T3-32</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>A-037</t>
+          <t>A-164</t>
         </is>
       </c>
       <c r="E89" s="15" t="n"/>
       <c r="F89" s="15" t="inlineStr">
         <is>
-          <t>A-010</t>
+          <t>A-162</t>
         </is>
       </c>
       <c r="G89" s="17" t="inlineStr">
         <is>
-          <t>Account Provisioning &amp; Deprovisioning Procedures</t>
+          <t>Competency Assessment Records</t>
         </is>
       </c>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I89" s="17" t="inlineStr">
         <is>
-          <t>Internal / CJIS</t>
+          <t>Confidential / CJIS</t>
         </is>
       </c>
       <c r="J89" s="15" t="inlineStr">
@@ -5305,7 +5325,7 @@
       </c>
       <c r="K89" s="17" t="inlineStr">
         <is>
-          <t>HR-aligned workflow for how every account is requested, approved, created, changed, and disabled, with roles per step and timing (e.g., access removed within a set window of departure). Documents the inactivity-detection automation that disables dormant accounts. Governs the provisioning/deprovisioning checklist and the review records.</t>
+          <t>Records that staff in technical and security-sensitive roles demonstrate competency, not just attendance: assessment, result, and any remediation. Supports certification and continuing-education tracking.</t>
         </is>
       </c>
       <c r="L89" s="17" t="n"/>
@@ -5323,33 +5343,33 @@
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>T3-34</t>
+          <t>T3-33</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>A-042</t>
+          <t>A-037</t>
         </is>
       </c>
       <c r="E90" s="15" t="n"/>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>A-095</t>
+          <t>A-010</t>
         </is>
       </c>
       <c r="G90" s="17" t="inlineStr">
         <is>
-          <t>Privileged &amp; Service Account Inventory</t>
+          <t>Account Provisioning &amp; Deprovisioning Procedures</t>
         </is>
       </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
-          <t>Restricted / CJIS</t>
+          <t>Internal / CJIS</t>
         </is>
       </c>
       <c r="J90" s="15" t="inlineStr">
@@ -5359,7 +5379,7 @@
       </c>
       <c r="K90" s="17" t="inlineStr">
         <is>
-          <t>Complete list of privileged and shared accounts, expanded to include service and cloud accounts: named custodians, systems in scope, an account-type field (user-admin, service, cloud), and rotation/review fields. The source for privileged-access monitoring and decommissioning.</t>
+          <t>HR-aligned workflow for how every account is requested, approved, created, changed, and disabled, with roles per step and timing (e.g., access removed within a set window of departure). Documents the inactivity-detection automation that disables dormant accounts. Governs the provisioning/deprovisioning checklist and the review records.</t>
         </is>
       </c>
       <c r="L90" s="17" t="n"/>
@@ -5372,38 +5392,38 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Tier 4</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>T4-01</t>
+          <t>T3-34</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>A-059</t>
+          <t>A-042</t>
         </is>
       </c>
       <c r="E91" s="15" t="n"/>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>A-057</t>
+          <t>A-095</t>
         </is>
       </c>
       <c r="G91" s="17" t="inlineStr">
         <is>
-          <t>Log Review Records</t>
+          <t>Privileged &amp; Service Account Inventory</t>
         </is>
       </c>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Restricted / CJIS</t>
         </is>
       </c>
       <c r="J91" s="15" t="inlineStr">
@@ -5413,7 +5433,7 @@
       </c>
       <c r="K91" s="17" t="inlineStr">
         <is>
-          <t>Dated evidence of completed log reviews: source, reviewer, period, findings, and escalation. Boundary: routine per-source log review; the periodic aggregate review meeting is recorded in Event Review Meeting Records.</t>
+          <t>Complete list of privileged and shared accounts, expanded to include service and cloud accounts: named custodians, systems in scope, an account-type field (user-admin, service, cloud), and rotation/review fields. The source for privileged-access monitoring and decommissioning.</t>
         </is>
       </c>
       <c r="L91" s="17" t="n"/>
@@ -5431,23 +5451,23 @@
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>T4-02</t>
+          <t>T4-01</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>A-137</t>
+          <t>A-059</t>
         </is>
       </c>
       <c r="E92" s="15" t="n"/>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>A-136</t>
+          <t>A-057</t>
         </is>
       </c>
       <c r="G92" s="17" t="inlineStr">
         <is>
-          <t>Event Review Meeting Records</t>
+          <t>Log Review Records</t>
         </is>
       </c>
       <c r="H92" s="17" t="inlineStr">
@@ -5467,7 +5487,7 @@
       </c>
       <c r="K92" s="17" t="inlineStr">
         <is>
-          <t>Dated record of the periodic aggregate security-event review meeting: attendees, data reviewed, significant findings, and actions. Boundary: periodic aggregate review meeting governed by the Security Event Review Procedures; routine per-source review is in Log Review Records.</t>
+          <t>Dated evidence of completed log reviews: source, reviewer, period, findings, and escalation. Boundary: routine per-source log review; the periodic aggregate review meeting is recorded in Event Review Meeting Records.</t>
         </is>
       </c>
       <c r="L92" s="17" t="n"/>
@@ -5485,33 +5505,33 @@
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>T4-03</t>
+          <t>T4-02</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>A-138</t>
+          <t>A-137</t>
         </is>
       </c>
       <c r="E93" s="15" t="n"/>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>A-057</t>
+          <t>A-136</t>
         </is>
       </c>
       <c r="G93" s="17" t="inlineStr">
         <is>
-          <t>NTP Configuration Documentation</t>
+          <t>Event Review Meeting Records</t>
         </is>
       </c>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I93" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J93" s="15" t="inlineStr">
@@ -5521,7 +5541,7 @@
       </c>
       <c r="K93" s="17" t="inlineStr">
         <is>
-          <t>As-built time synchronization: the authoritative time sources (secure NTP, GPS), which systems sync to them, authentication, acceptable drift thresholds, and failover. Includes SBCs and edge devices.</t>
+          <t>Dated record of the periodic aggregate security-event review meeting: attendees, data reviewed, significant findings, and actions. Boundary: periodic aggregate review meeting governed by the Security Event Review Procedures; routine per-source review is in Log Review Records.</t>
         </is>
       </c>
       <c r="L93" s="17" t="n"/>
@@ -5539,12 +5559,12 @@
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>T4-04</t>
+          <t>T4-03</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>A-139</t>
+          <t>A-138</t>
         </is>
       </c>
       <c r="E94" s="15" t="n"/>
@@ -5555,12 +5575,12 @@
       </c>
       <c r="G94" s="17" t="inlineStr">
         <is>
-          <t>Log Integrity Verification Procedures</t>
+          <t>NTP Configuration Documentation</t>
         </is>
       </c>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I94" s="17" t="inlineStr">
@@ -5575,7 +5595,7 @@
       </c>
       <c r="K94" s="17" t="inlineStr">
         <is>
-          <t>How tampered or missing logs are detected and prevented: write-once storage, HMAC/hash signing, ACL restrictions, and alerting on log gaps, so audit logs remain trustworthy for investigations.</t>
+          <t>As-built time synchronization: the authoritative time sources (secure NTP, GPS), which systems sync to them, authentication, acceptable drift thresholds, and failover. Includes SBCs and edge devices.</t>
         </is>
       </c>
       <c r="L94" s="17" t="n"/>
@@ -5593,28 +5613,28 @@
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>T4-05</t>
+          <t>T4-04</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>A-140</t>
+          <t>A-139</t>
         </is>
       </c>
       <c r="E95" s="15" t="n"/>
       <c r="F95" s="15" t="inlineStr">
         <is>
-          <t>A-138</t>
+          <t>A-057</t>
         </is>
       </c>
       <c r="G95" s="17" t="inlineStr">
         <is>
-          <t>Time Synchronization Audit Records</t>
+          <t>Log Integrity Verification Procedures</t>
         </is>
       </c>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I95" s="17" t="inlineStr">
@@ -5629,7 +5649,7 @@
       </c>
       <c r="K95" s="17" t="inlineStr">
         <is>
-          <t>Dated verification that log-generating systems are synchronized within acceptable drift, with outliers corrected and logged. Evidence behind timestamp integrity across systems.</t>
+          <t>How tampered or missing logs are detected and prevented: write-once storage, HMAC/hash signing, ACL restrictions, and alerting on log gaps, so audit logs remain trustworthy for investigations.</t>
         </is>
       </c>
       <c r="L95" s="17" t="n"/>
@@ -5647,33 +5667,33 @@
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>T4-06</t>
+          <t>T4-05</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>A-047</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F96" s="15" t="n"/>
+          <t>A-140</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="n"/>
+      <c r="F96" s="15" t="inlineStr">
+        <is>
+          <t>A-138</t>
+        </is>
+      </c>
       <c r="G96" s="17" t="inlineStr">
         <is>
-          <t>Network Architecture Diagram</t>
+          <t>Time Synchronization Audit Records</t>
         </is>
       </c>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>Architecture / Design</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J96" s="15" t="inlineStr">
@@ -5683,7 +5703,7 @@
       </c>
       <c r="K96" s="17" t="inlineStr">
         <is>
-          <t>Accurate, dated topology showing all segments, VLANs, devices, boundary points, and external connections. The foundation Phase 3 technical controls reference. Requires the asset inventory to be accurate.</t>
+          <t>Dated verification that log-generating systems are synchronized within acceptable drift, with outliers corrected and logged. Evidence behind timestamp integrity across systems.</t>
         </is>
       </c>
       <c r="L96" s="17" t="n"/>
@@ -5701,28 +5721,28 @@
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>T4-07</t>
+          <t>T4-06</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>A-103</t>
-        </is>
-      </c>
-      <c r="E97" s="15" t="n"/>
-      <c r="F97" s="15" t="inlineStr">
-        <is>
           <t>A-047</t>
         </is>
       </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F97" s="15" t="n"/>
       <c r="G97" s="17" t="inlineStr">
         <is>
-          <t>Firewall Ruleset Documentation</t>
+          <t>Network Architecture Diagram</t>
         </is>
       </c>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Architecture / Design</t>
         </is>
       </c>
       <c r="I97" s="17" t="inlineStr">
@@ -5737,7 +5757,7 @@
       </c>
       <c r="K97" s="17" t="inlineStr">
         <is>
-          <t>As-built firewall and perimeter rules: default-deny posture, the allow-list per zone with justification, and the review/removal process for obsolete rules. Covers SBCs and edge appliances. Change-controlled.</t>
+          <t>Accurate, dated topology showing all segments, VLANs, devices, boundary points, and external connections. The foundation Phase 3 technical controls reference. Requires the asset inventory to be accurate.</t>
         </is>
       </c>
       <c r="L97" s="17" t="n"/>
@@ -5755,23 +5775,23 @@
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>T4-08</t>
+          <t>T4-07</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>A-106</t>
+          <t>A-103</t>
         </is>
       </c>
       <c r="E98" s="15" t="n"/>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>A-105</t>
+          <t>A-047</t>
         </is>
       </c>
       <c r="G98" s="17" t="inlineStr">
         <is>
-          <t>IDS/IPS Configuration Records</t>
+          <t>Firewall Ruleset Documentation</t>
         </is>
       </c>
       <c r="H98" s="17" t="inlineStr">
@@ -5791,7 +5811,7 @@
       </c>
       <c r="K98" s="17" t="inlineStr">
         <is>
-          <t>As-built IDS/IPS: what is deployed, how it is tuned, signature/rule update management, and integrity-check cadence, under documented procedures. Alerts route to the Alert Triage &amp; Escalation Procedure.</t>
+          <t>As-built firewall and perimeter rules: default-deny posture, the allow-list per zone with justification, and the review/removal process for obsolete rules. Covers SBCs and edge appliances. Change-controlled.</t>
         </is>
       </c>
       <c r="L98" s="17" t="n"/>
@@ -5809,28 +5829,28 @@
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>T4-09</t>
+          <t>T4-08</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>A-121</t>
+          <t>A-106</t>
         </is>
       </c>
       <c r="E99" s="15" t="n"/>
       <c r="F99" s="15" t="inlineStr">
         <is>
-          <t>A-119</t>
+          <t>A-105</t>
         </is>
       </c>
       <c r="G99" s="17" t="inlineStr">
         <is>
-          <t>Service / Port Disablement Records</t>
+          <t>IDS/IPS Configuration Records</t>
         </is>
       </c>
       <c r="H99" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I99" s="17" t="inlineStr">
@@ -5845,7 +5865,7 @@
       </c>
       <c r="K99" s="17" t="inlineStr">
         <is>
-          <t>Per-system record of services, ports, and protocols explicitly disabled and the rationale (e.g., open Wi-Fi SSIDs, legacy protocols, auto script execution). Evidence behind endpoint hardening.</t>
+          <t>As-built IDS/IPS: what is deployed, how it is tuned, signature/rule update management, and integrity-check cadence, under documented procedures. Alerts route to the Alert Triage &amp; Escalation Procedure.</t>
         </is>
       </c>
       <c r="L99" s="17" t="n"/>
@@ -5863,28 +5883,28 @@
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>T4-10</t>
+          <t>T4-09</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>A-135</t>
+          <t>A-121</t>
         </is>
       </c>
       <c r="E100" s="15" t="n"/>
       <c r="F100" s="15" t="inlineStr">
         <is>
-          <t>A-133</t>
+          <t>A-119</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr">
         <is>
-          <t>Alert Triage &amp; Escalation Procedure</t>
+          <t>Service / Port Disablement Records</t>
         </is>
       </c>
       <c r="H100" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I100" s="17" t="inlineStr">
@@ -5899,7 +5919,7 @@
       </c>
       <c r="K100" s="17" t="inlineStr">
         <is>
-          <t>Alert triage and escalation for monitoring and network threat-detection alerts: trigger, triage, investigate, escalate, close, with severity tiers and notification paths. Covers IDS/IPS, host, and SIEM alerts.</t>
+          <t>Per-system record of services, ports, and protocols explicitly disabled and the rationale (e.g., open Wi-Fi SSIDs, legacy protocols, auto script execution). Evidence behind endpoint hardening.</t>
         </is>
       </c>
       <c r="L100" s="17" t="n"/>
@@ -5917,23 +5937,23 @@
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>T4-11</t>
+          <t>T4-10</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
         <is>
-          <t>A-055</t>
+          <t>A-135</t>
         </is>
       </c>
       <c r="E101" s="15" t="n"/>
       <c r="F101" s="15" t="inlineStr">
         <is>
-          <t>A-052</t>
+          <t>A-133</t>
         </is>
       </c>
       <c r="G101" s="17" t="inlineStr">
         <is>
-          <t>Patch Testing Procedure</t>
+          <t>Alert Triage &amp; Escalation Procedure</t>
         </is>
       </c>
       <c r="H101" s="17" t="inlineStr">
@@ -5943,7 +5963,7 @@
       </c>
       <c r="I101" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J101" s="15" t="inlineStr">
@@ -5953,7 +5973,7 @@
       </c>
       <c r="K101" s="17" t="inlineStr">
         <is>
-          <t>How OS and application updates are tested in a non-production environment before deployment to dispatch systems, including authenticity checks and post-deployment integrity verification.</t>
+          <t>Alert triage and escalation for monitoring and network threat-detection alerts: trigger, triage, investigate, escalate, close, with severity tiers and notification paths. Covers IDS/IPS, host, and SIEM alerts.</t>
         </is>
       </c>
       <c r="L101" s="17" t="n"/>
@@ -5971,12 +5991,12 @@
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>T4-12</t>
+          <t>T4-11</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>A-054</t>
+          <t>A-055</t>
         </is>
       </c>
       <c r="E102" s="15" t="n"/>
@@ -5987,17 +6007,17 @@
       </c>
       <c r="G102" s="17" t="inlineStr">
         <is>
-          <t>Patch Management Schedule &amp; Tracking Log</t>
+          <t>Patch Testing Procedure</t>
         </is>
       </c>
       <c r="H102" s="17" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J102" s="15" t="inlineStr">
@@ -6007,7 +6027,7 @@
       </c>
       <c r="K102" s="17" t="inlineStr">
         <is>
-          <t>Patching frequency by system type and criticality, with CAD/RMS-specific testing before deployment, and a tracking log of patches applied (date, approver, outcome). Requires the asset inventory and the change policy.</t>
+          <t>How OS and application updates are tested in a non-production environment before deployment to dispatch systems, including authenticity checks and post-deployment integrity verification.</t>
         </is>
       </c>
       <c r="L102" s="17" t="n"/>
@@ -6025,12 +6045,12 @@
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>T4-13</t>
+          <t>T4-12</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
-          <t>A-053</t>
+          <t>A-054</t>
         </is>
       </c>
       <c r="E103" s="15" t="n"/>
@@ -6041,17 +6061,17 @@
       </c>
       <c r="G103" s="17" t="inlineStr">
         <is>
-          <t>Change Request &amp; Approval Log</t>
+          <t>Patch Management Schedule &amp; Tracking Log</t>
         </is>
       </c>
       <c r="H103" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="I103" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J103" s="15" t="inlineStr">
@@ -6061,7 +6081,7 @@
       </c>
       <c r="K103" s="17" t="inlineStr">
         <is>
-          <t>Record of every change request: description, risk/impact assessment, approver, schedule, and outcome. The evidence the Change Management Policy runs on.</t>
+          <t>Patching frequency by system type and criticality, with CAD/RMS-specific testing before deployment, and a tracking log of patches applied (date, approver, outcome). Requires the asset inventory and the change policy.</t>
         </is>
       </c>
       <c r="L103" s="17" t="n"/>
@@ -6079,12 +6099,12 @@
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>T4-14</t>
+          <t>T4-13</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>A-122</t>
+          <t>A-053</t>
         </is>
       </c>
       <c r="E104" s="15" t="n"/>
@@ -6095,12 +6115,12 @@
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
-          <t>Emergency Change Procedures</t>
+          <t>Change Request &amp; Approval Log</t>
         </is>
       </c>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I104" s="17" t="inlineStr">
@@ -6115,7 +6135,7 @@
       </c>
       <c r="K104" s="17" t="inlineStr">
         <is>
-          <t>Expedited approval path for critical patches or changes that cannot wait for the normal cycle: who authorizes, what is documented, and how it is reconciled back into change management.</t>
+          <t>Record of every change request: description, risk/impact assessment, approver, schedule, and outcome. The evidence the Change Management Policy runs on.</t>
         </is>
       </c>
       <c r="L104" s="17" t="n"/>
@@ -6133,33 +6153,33 @@
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>T4-15</t>
+          <t>T4-14</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
         <is>
-          <t>A-127</t>
+          <t>A-122</t>
         </is>
       </c>
       <c r="E105" s="15" t="n"/>
       <c r="F105" s="15" t="inlineStr">
         <is>
-          <t>A-129</t>
+          <t>A-052</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr">
         <is>
-          <t>Certificate Inventory</t>
+          <t>Emergency Change Procedures</t>
         </is>
       </c>
       <c r="H105" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I105" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J105" s="15" t="inlineStr">
@@ -6169,7 +6189,7 @@
       </c>
       <c r="K105" s="17" t="inlineStr">
         <is>
-          <t>Every TLS/SSL and other certificate in use: issuer, subject/system, expiration, and responsible owner, including any self-signed exceptions. Supports renewal-before-expiry and availability in DR. Governed by the Key &amp; Certificate Management Policy.</t>
+          <t>Expedited approval path for critical patches or changes that cannot wait for the normal cycle: who authorizes, what is documented, and how it is reconciled back into change management.</t>
         </is>
       </c>
       <c r="L105" s="17" t="n"/>
@@ -6187,12 +6207,12 @@
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>T4-16</t>
+          <t>T4-15</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>A-128</t>
+          <t>A-127</t>
         </is>
       </c>
       <c r="E106" s="15" t="n"/>
@@ -6203,17 +6223,17 @@
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>Certificate Renewal &amp; Revocation Procedures</t>
+          <t>Certificate Inventory</t>
         </is>
       </c>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J106" s="15" t="inlineStr">
@@ -6223,7 +6243,7 @@
       </c>
       <c r="K106" s="17" t="inlineStr">
         <is>
-          <t>How certificates are requested, approved, renewed before expiry (with notification triggers), and revoked, and how chains are validated at runtime (CRL/OCSP) with failures logged to the SIEM. Implements the Key &amp; Certificate Management Policy.</t>
+          <t>Every TLS/SSL and other certificate in use: issuer, subject/system, expiration, and responsible owner, including any self-signed exceptions. Supports renewal-before-expiry and availability in DR. Governed by the Key &amp; Certificate Management Policy.</t>
         </is>
       </c>
       <c r="L106" s="17" t="n"/>
@@ -6241,33 +6261,33 @@
       </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
-          <t>T4-17</t>
+          <t>T4-16</t>
         </is>
       </c>
       <c r="D107" s="16" t="inlineStr">
         <is>
-          <t>A-134</t>
+          <t>A-128</t>
         </is>
       </c>
       <c r="E107" s="15" t="n"/>
       <c r="F107" s="15" t="inlineStr">
         <is>
-          <t>A-133</t>
+          <t>A-129</t>
         </is>
       </c>
       <c r="G107" s="17" t="inlineStr">
         <is>
-          <t>SIEM / Monitoring Tool Configuration Records</t>
+          <t>Certificate Renewal &amp; Revocation Procedures</t>
         </is>
       </c>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I107" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J107" s="15" t="inlineStr">
@@ -6277,7 +6297,7 @@
       </c>
       <c r="K107" s="17" t="inlineStr">
         <is>
-          <t>As-built central monitoring: the SIEM and other tools deployed, log sources ingested, correlation rules, tuning, and who manages them. Boundary: the central SIEM/monitoring platform; per-system session-capture settings are in Session Monitoring Configuration Records.</t>
+          <t>How certificates are requested, approved, renewed before expiry (with notification triggers), and revoked, and how chains are validated at runtime (CRL/OCSP) with failures logged to the SIEM. Implements the Key &amp; Certificate Management Policy.</t>
         </is>
       </c>
       <c r="L107" s="17" t="n"/>
@@ -6295,28 +6315,28 @@
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>T4-18</t>
+          <t>T4-17</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>A-130</t>
+          <t>A-134</t>
         </is>
       </c>
       <c r="E108" s="15" t="n"/>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>A-129</t>
+          <t>A-133</t>
         </is>
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>Key Inventory &amp; Custody Records</t>
+          <t>SIEM / Monitoring Tool Configuration Records</t>
         </is>
       </c>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I108" s="17" t="inlineStr">
@@ -6331,7 +6351,7 @@
       </c>
       <c r="K108" s="17" t="inlineStr">
         <is>
-          <t>Every key or key class with named custodian and backup custodian, the systems it protects, and dedicated keys for special uses (log-integrity, device certificates). The custody record behind key governance.</t>
+          <t>As-built central monitoring: the SIEM and other tools deployed, log sources ingested, correlation rules, tuning, and who manages them. Boundary: the central SIEM/monitoring platform; per-system session-capture settings are in Session Monitoring Configuration Records.</t>
         </is>
       </c>
       <c r="L108" s="17" t="n"/>
@@ -6349,12 +6369,12 @@
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>T4-19</t>
+          <t>T4-18</t>
         </is>
       </c>
       <c r="D109" s="16" t="inlineStr">
         <is>
-          <t>A-132</t>
+          <t>A-130</t>
         </is>
       </c>
       <c r="E109" s="15" t="n"/>
@@ -6365,12 +6385,12 @@
       </c>
       <c r="G109" s="17" t="inlineStr">
         <is>
-          <t>Key Escrow and Recovery Procedure</t>
+          <t>Key Inventory &amp; Custody Records</t>
         </is>
       </c>
       <c r="H109" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I109" s="17" t="inlineStr">
@@ -6385,7 +6405,7 @@
       </c>
       <c r="K109" s="17" t="inlineStr">
         <is>
-          <t>How keys are backed up or escrowed and recovered if a custodian is unavailable or a system fails, including dual-control retrieval, so encrypted data and operations remain available during outages and DR.</t>
+          <t>Every key or key class with named custodian and backup custodian, the systems it protects, and dedicated keys for special uses (log-integrity, device certificates). The custody record behind key governance.</t>
         </is>
       </c>
       <c r="L109" s="17" t="n"/>
@@ -6403,12 +6423,12 @@
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>T4-20</t>
+          <t>T4-19</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>A-131</t>
+          <t>A-132</t>
         </is>
       </c>
       <c r="E110" s="15" t="n"/>
@@ -6419,12 +6439,12 @@
       </c>
       <c r="G110" s="17" t="inlineStr">
         <is>
-          <t>Key Rotation Schedule</t>
+          <t>Key Escrow and Recovery Procedure</t>
         </is>
       </c>
       <c r="H110" s="17" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I110" s="17" t="inlineStr">
@@ -6439,7 +6459,7 @@
       </c>
       <c r="K110" s="17" t="inlineStr">
         <is>
-          <t>Rotation frequency by key type and a record of completed rotations. Lists key/class, frequency, last rotated, next due, owner, with escalation for missed rotations.</t>
+          <t>How keys are backed up or escrowed and recovered if a custodian is unavailable or a system fails, including dual-control retrieval, so encrypted data and operations remain available during outages and DR.</t>
         </is>
       </c>
       <c r="L110" s="17" t="n"/>
@@ -6457,32 +6477,28 @@
       </c>
       <c r="C111" s="15" t="inlineStr">
         <is>
-          <t>T4-21</t>
+          <t>T4-20</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
         <is>
-          <t>A-166</t>
-        </is>
-      </c>
-      <c r="E111" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>A-131</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="n"/>
       <c r="F111" s="15" t="inlineStr">
         <is>
-          <t>A-012</t>
+          <t>A-129</t>
         </is>
       </c>
       <c r="G111" s="17" t="inlineStr">
         <is>
-          <t>Document Handling Standard</t>
+          <t>Key Rotation Schedule</t>
         </is>
       </c>
       <c r="H111" s="17" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="I111" s="17" t="inlineStr">
@@ -6497,7 +6513,7 @@
       </c>
       <c r="K111" s="17" t="inlineStr">
         <is>
-          <t>Defines handling, storage, transmission, transport, and destruction requirements for each data classification, including removable and portable media (drives, tapes, printed reports) and a media tracking register. Implements the Data Classification Policy; carries the secure-transmission and media rules referenced across 3.B.</t>
+          <t>Rotation frequency by key type and a record of completed rotations. Lists key/class, frequency, last rotated, next due, owner, with escalation for missed rotations.</t>
         </is>
       </c>
       <c r="L111" s="17" t="n"/>
@@ -6515,15 +6531,19 @@
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>T4-22</t>
+          <t>T4-21</t>
         </is>
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>A-045</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="n"/>
+          <t>A-166</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
           <t>A-012</t>
@@ -6531,17 +6551,17 @@
       </c>
       <c r="G112" s="17" t="inlineStr">
         <is>
-          <t>Secure Disposal Procedures</t>
+          <t>Document Handling Standard</t>
         </is>
       </c>
       <c r="H112" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I112" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J112" s="15" t="inlineStr">
@@ -6551,7 +6571,7 @@
       </c>
       <c r="K112" s="17" t="inlineStr">
         <is>
-          <t>How data and storage media are securely destroyed at end of retention, by classification: methods (cryptographic wipe, overwrite, shredding), authorization, and the destruction record produced. Covers end-of-life hardware and software decommissioning.</t>
+          <t>Defines handling, storage, transmission, transport, and destruction requirements for each data classification, including removable and portable media (drives, tapes, printed reports) and a media tracking register. Implements the Data Classification Policy; carries the secure-transmission and media rules referenced across 3.B.</t>
         </is>
       </c>
       <c r="L112" s="17" t="n"/>
@@ -6569,28 +6589,28 @@
       </c>
       <c r="C113" s="15" t="inlineStr">
         <is>
-          <t>T4-23</t>
+          <t>T4-22</t>
         </is>
       </c>
       <c r="D113" s="16" t="inlineStr">
         <is>
-          <t>A-101</t>
+          <t>A-045</t>
         </is>
       </c>
       <c r="E113" s="15" t="n"/>
       <c r="F113" s="15" t="inlineStr">
         <is>
-          <t>A-045</t>
+          <t>A-012</t>
         </is>
       </c>
       <c r="G113" s="17" t="inlineStr">
         <is>
-          <t>Data Disposal / Destruction Records</t>
+          <t>Secure Disposal Procedures</t>
         </is>
       </c>
       <c r="H113" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I113" s="17" t="inlineStr">
@@ -6605,7 +6625,7 @@
       </c>
       <c r="K113" s="17" t="inlineStr">
         <is>
-          <t>Dated evidence of completed destructions: item, classification, method, operator, and certificate of destruction where applicable. The evidence side of the Secure Disposal Procedures.</t>
+          <t>How data and storage media are securely destroyed at end of retention, by classification: methods (cryptographic wipe, overwrite, shredding), authorization, and the destruction record produced. Covers end-of-life hardware and software decommissioning.</t>
         </is>
       </c>
       <c r="L113" s="17" t="n"/>
@@ -6623,33 +6643,33 @@
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>T4-24</t>
+          <t>T4-23</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
         <is>
-          <t>A-040</t>
+          <t>A-101</t>
         </is>
       </c>
       <c r="E114" s="15" t="n"/>
       <c r="F114" s="15" t="inlineStr">
         <is>
-          <t>A-039</t>
+          <t>A-045</t>
         </is>
       </c>
       <c r="G114" s="17" t="inlineStr">
         <is>
-          <t>MFA Implementation Record</t>
+          <t>Data Disposal / Destruction Records</t>
         </is>
       </c>
       <c r="H114" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I114" s="17" t="inlineStr">
         <is>
-          <t>Restricted / CJIS</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J114" s="15" t="inlineStr">
@@ -6659,7 +6679,7 @@
       </c>
       <c r="K114" s="17" t="inlineStr">
         <is>
-          <t>System-by-system record of where MFA is enforced, the method (authenticator app, hardware token, one-time code), and any documented exceptions with rationale. Covers remote, on-premises, and cloud, for privileged and non-privileged accounts.</t>
+          <t>Dated evidence of completed destructions: item, classification, method, operator, and certificate of destruction where applicable. The evidence side of the Secure Disposal Procedures.</t>
         </is>
       </c>
       <c r="L114" s="17" t="n"/>
@@ -6677,12 +6697,12 @@
       </c>
       <c r="C115" s="15" t="inlineStr">
         <is>
-          <t>T4-25</t>
+          <t>T4-24</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
         <is>
-          <t>A-041</t>
+          <t>A-040</t>
         </is>
       </c>
       <c r="E115" s="15" t="n"/>
@@ -6693,12 +6713,12 @@
       </c>
       <c r="G115" s="17" t="inlineStr">
         <is>
-          <t>Default Credential Remediation Log</t>
+          <t>MFA Implementation Record</t>
         </is>
       </c>
       <c r="H115" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I115" s="17" t="inlineStr">
@@ -6713,7 +6733,7 @@
       </c>
       <c r="K115" s="17" t="inlineStr">
         <is>
-          <t>Tracks replacement of vendor-default credentials on every new system before it goes live: system, default removed, date, and verifier. Evidence that defaults are eliminated at deployment.</t>
+          <t>System-by-system record of where MFA is enforced, the method (authenticator app, hardware token, one-time code), and any documented exceptions with rationale. Covers remote, on-premises, and cloud, for privileged and non-privileged accounts.</t>
         </is>
       </c>
       <c r="L115" s="17" t="n"/>
@@ -6731,28 +6751,28 @@
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>T4-26</t>
+          <t>T4-25</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>A-098</t>
+          <t>A-041</t>
         </is>
       </c>
       <c r="E116" s="15" t="n"/>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>A-097</t>
+          <t>A-039</t>
         </is>
       </c>
       <c r="G116" s="17" t="inlineStr">
         <is>
-          <t>Session Monitoring Configuration Records</t>
+          <t>Default Credential Remediation Log</t>
         </is>
       </c>
       <c r="H116" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I116" s="17" t="inlineStr">
@@ -6767,7 +6787,7 @@
       </c>
       <c r="K116" s="17" t="inlineStr">
         <is>
-          <t>Documents session-capture settings on access systems: which session events are recorded (logins, failures, privilege changes), timeout values as configured, and alerting for unusual behavior. Boundary: session-capture settings on access systems; the central platform is documented in SIEM / Monitoring Tool Configuration Records.</t>
+          <t>Tracks replacement of vendor-default credentials on every new system before it goes live: system, default removed, date, and verifier. Evidence that defaults are eliminated at deployment.</t>
         </is>
       </c>
       <c r="L116" s="17" t="n"/>
@@ -6785,33 +6805,33 @@
       </c>
       <c r="C117" s="15" t="inlineStr">
         <is>
-          <t>T4-27</t>
+          <t>T4-26</t>
         </is>
       </c>
       <c r="D117" s="16" t="inlineStr">
         <is>
-          <t>A-034</t>
+          <t>A-098</t>
         </is>
       </c>
       <c r="E117" s="15" t="n"/>
       <c r="F117" s="15" t="inlineStr">
         <is>
-          <t>A-010</t>
+          <t>A-097</t>
         </is>
       </c>
       <c r="G117" s="17" t="inlineStr">
         <is>
-          <t>System Access Request &amp; Approval Forms</t>
+          <t>Session Monitoring Configuration Records</t>
         </is>
       </c>
       <c r="H117" s="17" t="inlineStr">
         <is>
-          <t>Agreement / Form</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I117" s="17" t="inlineStr">
         <is>
-          <t>Confidential / CJIS</t>
+          <t>Restricted / CJIS</t>
         </is>
       </c>
       <c r="J117" s="15" t="inlineStr">
@@ -6821,7 +6841,7 @@
       </c>
       <c r="K117" s="17" t="inlineStr">
         <is>
-          <t>Standardized form to initiate, document, and authorize any access grant or change: requester, role, systems, justification, approver, and date. The operational front end of the Access Control Policy and the request path for temporary privilege elevation.</t>
+          <t>Documents session-capture settings on access systems: which session events are recorded (logins, failures, privilege changes), timeout values as configured, and alerting for unusual behavior. Boundary: session-capture settings on access systems; the central platform is documented in SIEM / Monitoring Tool Configuration Records.</t>
         </is>
       </c>
       <c r="L117" s="17" t="n"/>
@@ -6839,12 +6859,12 @@
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>T4-28</t>
+          <t>T4-27</t>
         </is>
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>A-095</t>
+          <t>A-034</t>
         </is>
       </c>
       <c r="E118" s="15" t="n"/>
@@ -6855,17 +6875,17 @@
       </c>
       <c r="G118" s="17" t="inlineStr">
         <is>
-          <t>Privileged Access Management (PAM) Policy</t>
+          <t>System Access Request &amp; Approval Forms</t>
         </is>
       </c>
       <c r="H118" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Agreement / Form</t>
         </is>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
-          <t>Internal / CJIS</t>
+          <t>Confidential / CJIS</t>
         </is>
       </c>
       <c r="J118" s="15" t="inlineStr">
@@ -6875,7 +6895,7 @@
       </c>
       <c r="K118" s="17" t="inlineStr">
         <is>
-          <t>Governs how privileged accounts are requested, approved, used, logged, reviewed, and decommissioned, including enhanced behavior rules and accountability for misuse. Includes a Temporary Privilege Elevation section (time-limited, auto-expiring access requested and approved through the System Access Request &amp; Approval Forms). Requires unique identification, stronger authentication, and specialized training for privileged users.</t>
+          <t>Standardized form to initiate, document, and authorize any access grant or change: requester, role, systems, justification, approver, and date. The operational front end of the Access Control Policy and the request path for temporary privilege elevation.</t>
         </is>
       </c>
       <c r="L118" s="17" t="n"/>
@@ -6893,33 +6913,33 @@
       </c>
       <c r="C119" s="15" t="inlineStr">
         <is>
-          <t>T4-29</t>
+          <t>T4-28</t>
         </is>
       </c>
       <c r="D119" s="16" t="inlineStr">
         <is>
-          <t>A-096</t>
+          <t>A-095</t>
         </is>
       </c>
       <c r="E119" s="15" t="n"/>
       <c r="F119" s="15" t="inlineStr">
         <is>
-          <t>A-095</t>
+          <t>A-010</t>
         </is>
       </c>
       <c r="G119" s="17" t="inlineStr">
         <is>
-          <t>Privileged Access Review Records</t>
+          <t>Privileged Access Management (PAM) Policy</t>
         </is>
       </c>
       <c r="H119" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I119" s="17" t="inlineStr">
         <is>
-          <t>Confidential / CJIS</t>
+          <t>Internal / CJIS</t>
         </is>
       </c>
       <c r="J119" s="15" t="inlineStr">
@@ -6929,7 +6949,7 @@
       </c>
       <c r="K119" s="17" t="inlineStr">
         <is>
-          <t>Dated record of privileged-access reviews and revocations of unused or unnecessary elevated rights (privilege creep), plus review of recorded privileged sessions for misuse or anomalous activity.</t>
+          <t>Governs how privileged accounts are requested, approved, used, logged, reviewed, and decommissioned, including enhanced behavior rules and accountability for misuse. Includes a Temporary Privilege Elevation section (time-limited, auto-expiring access requested and approved through the System Access Request &amp; Approval Forms). Requires unique identification, stronger authentication, and specialized training for privileged users.</t>
         </is>
       </c>
       <c r="L119" s="17" t="n"/>
@@ -6947,33 +6967,33 @@
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>T4-30</t>
+          <t>T4-29</t>
         </is>
       </c>
       <c r="D120" s="16" t="inlineStr">
         <is>
-          <t>A-145</t>
+          <t>A-096</t>
         </is>
       </c>
       <c r="E120" s="15" t="n"/>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>A-143</t>
+          <t>A-095</t>
         </is>
       </c>
       <c r="G120" s="17" t="inlineStr">
         <is>
-          <t>Single-Point-of-Failure Assessment Record</t>
+          <t>Privileged Access Review Records</t>
         </is>
       </c>
       <c r="H120" s="17" t="inlineStr">
         <is>
-          <t>Report / Assessment</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Confidential / CJIS</t>
         </is>
       </c>
       <c r="J120" s="15" t="inlineStr">
@@ -6983,7 +7003,7 @@
       </c>
       <c r="K120" s="17" t="inlineStr">
         <is>
-          <t>Periodic review identifying systems or paths without redundancy (cabling, power, core switch), with risk treatment decisions and prioritization.</t>
+          <t>Dated record of privileged-access reviews and revocations of unused or unnecessary elevated rights (privilege creep), plus review of recorded privileged sessions for misuse or anomalous activity.</t>
         </is>
       </c>
       <c r="L120" s="17" t="n"/>
@@ -7001,23 +7021,23 @@
       </c>
       <c r="C121" s="15" t="inlineStr">
         <is>
-          <t>T4-31</t>
+          <t>T4-30</t>
         </is>
       </c>
       <c r="D121" s="16" t="inlineStr">
         <is>
-          <t>A-146</t>
+          <t>A-145</t>
         </is>
       </c>
       <c r="E121" s="15" t="n"/>
       <c r="F121" s="15" t="inlineStr">
         <is>
-          <t>A-020</t>
+          <t>A-143</t>
         </is>
       </c>
       <c r="G121" s="17" t="inlineStr">
         <is>
-          <t>RTO Compliance Matrix</t>
+          <t>Single-Point-of-Failure Assessment Record</t>
         </is>
       </c>
       <c r="H121" s="17" t="inlineStr">
@@ -7037,7 +7057,7 @@
       </c>
       <c r="K121" s="17" t="inlineStr">
         <is>
-          <t>Maps actual tested recovery times against the RTOs in the RTO/RPO Documentation, with gaps and remediation plans. Confirms whether recovery targets are being met.</t>
+          <t>Periodic review identifying systems or paths without redundancy (cabling, power, core switch), with risk treatment decisions and prioritization.</t>
         </is>
       </c>
       <c r="L121" s="17" t="n"/>
@@ -7055,24 +7075,28 @@
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>T4-32</t>
+          <t>T4-31</t>
         </is>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>A-068</t>
+          <t>A-146</t>
         </is>
       </c>
       <c r="E122" s="15" t="n"/>
-      <c r="F122" s="15" t="n"/>
+      <c r="F122" s="15" t="inlineStr">
+        <is>
+          <t>A-020</t>
+        </is>
+      </c>
       <c r="G122" s="17" t="inlineStr">
         <is>
-          <t>UPS / Generator Test Records</t>
+          <t>RTO Compliance Matrix</t>
         </is>
       </c>
       <c r="H122" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Report / Assessment</t>
         </is>
       </c>
       <c r="I122" s="17" t="inlineStr">
@@ -7087,7 +7111,7 @@
       </c>
       <c r="K122" s="17" t="inlineStr">
         <is>
-          <t>Dated evidence of regular power-resilience testing: generator load tests, UPS battery capacity verification, and any fallback (portable generators). Frequency per the power resilience configuration.</t>
+          <t>Maps actual tested recovery times against the RTOs in the RTO/RPO Documentation, with gaps and remediation plans. Confirms whether recovery targets are being met.</t>
         </is>
       </c>
       <c r="L122" s="17" t="n"/>
@@ -7105,28 +7129,24 @@
       </c>
       <c r="C123" s="15" t="inlineStr">
         <is>
-          <t>T4-33</t>
+          <t>T4-32</t>
         </is>
       </c>
       <c r="D123" s="16" t="inlineStr">
         <is>
-          <t>A-147</t>
+          <t>A-068</t>
         </is>
       </c>
       <c r="E123" s="15" t="n"/>
-      <c r="F123" s="15" t="inlineStr">
-        <is>
-          <t>A-019</t>
-        </is>
-      </c>
+      <c r="F123" s="15" t="n"/>
       <c r="G123" s="17" t="inlineStr">
         <is>
-          <t>Power Resilience Configuration Documentation</t>
+          <t>UPS / Generator Test Records</t>
         </is>
       </c>
       <c r="H123" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I123" s="17" t="inlineStr">
@@ -7141,7 +7161,7 @@
       </c>
       <c r="K123" s="17" t="inlineStr">
         <is>
-          <t>As-built power resilience: UPS and generator capacity relative to the systems they protect, runtime at full load, managed-shutdown procedure beyond generator runtime, and self-contained or limited-capability alternatives for extended outages.</t>
+          <t>Dated evidence of regular power-resilience testing: generator load tests, UPS battery capacity verification, and any fallback (portable generators). Frequency per the power resilience configuration.</t>
         </is>
       </c>
       <c r="L123" s="17" t="n"/>
@@ -7159,19 +7179,23 @@
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>T4-34</t>
+          <t>T4-33</t>
         </is>
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>A-153</t>
+          <t>A-147</t>
         </is>
       </c>
       <c r="E124" s="15" t="n"/>
-      <c r="F124" s="15" t="n"/>
+      <c r="F124" s="15" t="inlineStr">
+        <is>
+          <t>A-019</t>
+        </is>
+      </c>
       <c r="G124" s="17" t="inlineStr">
         <is>
-          <t>Environmental Sensor Inventory &amp; Alert Configuration</t>
+          <t>Power Resilience Configuration Documentation</t>
         </is>
       </c>
       <c r="H124" s="17" t="inlineStr">
@@ -7191,7 +7215,7 @@
       </c>
       <c r="K124" s="17" t="inlineStr">
         <is>
-          <t>Inventory of temperature, humidity, water-detection, and smoke/fire sensors in critical spaces, their monitoring method, alert thresholds, and notification routing (SMS, paging, dashboard).</t>
+          <t>As-built power resilience: UPS and generator capacity relative to the systems they protect, runtime at full load, managed-shutdown procedure beyond generator runtime, and self-contained or limited-capability alternatives for extended outages.</t>
         </is>
       </c>
       <c r="L124" s="17" t="n"/>
@@ -7209,33 +7233,29 @@
       </c>
       <c r="C125" s="15" t="inlineStr">
         <is>
-          <t>T4-35</t>
+          <t>T4-34</t>
         </is>
       </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
-          <t>A-154</t>
+          <t>A-153</t>
         </is>
       </c>
       <c r="E125" s="15" t="n"/>
-      <c r="F125" s="15" t="inlineStr">
-        <is>
-          <t>A-153</t>
-        </is>
-      </c>
+      <c r="F125" s="15" t="n"/>
       <c r="G125" s="17" t="inlineStr">
         <is>
-          <t>Environmental Monitoring Log</t>
+          <t>Environmental Sensor Inventory &amp; Alert Configuration</t>
         </is>
       </c>
       <c r="H125" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I125" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J125" s="15" t="inlineStr">
@@ -7245,7 +7265,7 @@
       </c>
       <c r="K125" s="17" t="inlineStr">
         <is>
-          <t>Dated record of environmental alerts and responses: what triggered, who was notified, and how it was resolved, plus sensor health checks.</t>
+          <t>Inventory of temperature, humidity, water-detection, and smoke/fire sensors in critical spaces, their monitoring method, alert thresholds, and notification routing (SMS, paging, dashboard).</t>
         </is>
       </c>
       <c r="L125" s="17" t="n"/>
@@ -7263,28 +7283,28 @@
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>T4-36</t>
+          <t>T4-35</t>
         </is>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>A-073</t>
+          <t>A-154</t>
         </is>
       </c>
       <c r="E126" s="15" t="n"/>
       <c r="F126" s="15" t="inlineStr">
         <is>
-          <t>A-069</t>
+          <t>A-153</t>
         </is>
       </c>
       <c r="G126" s="17" t="inlineStr">
         <is>
-          <t>Vendor Access Coordination Procedure</t>
+          <t>Environmental Monitoring Log</t>
         </is>
       </c>
       <c r="H126" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I126" s="17" t="inlineStr">
@@ -7299,7 +7319,7 @@
       </c>
       <c r="K126" s="17" t="inlineStr">
         <is>
-          <t>How vendor site visits to equipment areas are pre-authorized, scheduled, escorted, and logged, including identity verification and the conditions for unescorted access.</t>
+          <t>Dated record of environmental alerts and responses: what triggered, who was notified, and how it was resolved, plus sensor health checks.</t>
         </is>
       </c>
       <c r="L126" s="17" t="n"/>
@@ -7317,12 +7337,12 @@
       </c>
       <c r="C127" s="15" t="inlineStr">
         <is>
-          <t>T4-37</t>
+          <t>T4-36</t>
         </is>
       </c>
       <c r="D127" s="16" t="inlineStr">
         <is>
-          <t>A-071</t>
+          <t>A-073</t>
         </is>
       </c>
       <c r="E127" s="15" t="n"/>
@@ -7333,17 +7353,17 @@
       </c>
       <c r="G127" s="17" t="inlineStr">
         <is>
-          <t>Visitor Log</t>
+          <t>Vendor Access Coordination Procedure</t>
         </is>
       </c>
       <c r="H127" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I127" s="17" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J127" s="15" t="inlineStr">
@@ -7353,7 +7373,7 @@
       </c>
       <c r="K127" s="17" t="inlineStr">
         <is>
-          <t>Record of every visitor to controlled areas: name, purpose, escort, and entry/exit times. Reviewed for anomalies (after-hours visits) per incident procedures.</t>
+          <t>How vendor site visits to equipment areas are pre-authorized, scheduled, escorted, and logged, including identity verification and the conditions for unescorted access.</t>
         </is>
       </c>
       <c r="L127" s="17" t="n"/>
@@ -7371,12 +7391,12 @@
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>T4-38</t>
+          <t>T4-37</t>
         </is>
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>A-072</t>
+          <t>A-071</t>
         </is>
       </c>
       <c r="E128" s="15" t="n"/>
@@ -7387,12 +7407,12 @@
       </c>
       <c r="G128" s="17" t="inlineStr">
         <is>
-          <t>Visitor Access Agreement Form</t>
+          <t>Visitor Log</t>
         </is>
       </c>
       <c r="H128" s="17" t="inlineStr">
         <is>
-          <t>Agreement / Form</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I128" s="17" t="inlineStr">
@@ -7407,7 +7427,7 @@
       </c>
       <c r="K128" s="17" t="inlineStr">
         <is>
-          <t>Signed acknowledgment by visitors of the PSAP's access rules and any confidentiality requirements, retained per visit.</t>
+          <t>Record of every visitor to controlled areas: name, purpose, escort, and entry/exit times. Reviewed for anomalies (after-hours visits) per incident procedures.</t>
         </is>
       </c>
       <c r="L128" s="17" t="n"/>
@@ -7425,12 +7445,12 @@
       </c>
       <c r="C129" s="15" t="inlineStr">
         <is>
-          <t>T4-39</t>
+          <t>T4-38</t>
         </is>
       </c>
       <c r="D129" s="16" t="inlineStr">
         <is>
-          <t>A-151</t>
+          <t>A-072</t>
         </is>
       </c>
       <c r="E129" s="15" t="n"/>
@@ -7441,17 +7461,17 @@
       </c>
       <c r="G129" s="17" t="inlineStr">
         <is>
-          <t>Camera and Sensor Maintenance Record</t>
+          <t>Visitor Access Agreement Form</t>
         </is>
       </c>
       <c r="H129" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Agreement / Form</t>
         </is>
       </c>
       <c r="I129" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="J129" s="15" t="inlineStr">
@@ -7461,7 +7481,7 @@
       </c>
       <c r="K129" s="17" t="inlineStr">
         <is>
-          <t>Dated verification that cameras, badge readers, and door sensors are functioning and recording correctly, with retention settings confirmed and faults remediated.</t>
+          <t>Signed acknowledgment by visitors of the PSAP's access rules and any confidentiality requirements, retained per visit.</t>
         </is>
       </c>
       <c r="L129" s="17" t="n"/>
@@ -7479,23 +7499,23 @@
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>T4-40</t>
+          <t>T4-39</t>
         </is>
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>A-026</t>
+          <t>A-151</t>
         </is>
       </c>
       <c r="E130" s="15" t="n"/>
       <c r="F130" s="15" t="inlineStr">
         <is>
-          <t>A-086</t>
+          <t>A-069</t>
         </is>
       </c>
       <c r="G130" s="17" t="inlineStr">
         <is>
-          <t>CJIS Security Awareness Training Completion Record</t>
+          <t>Camera and Sensor Maintenance Record</t>
         </is>
       </c>
       <c r="H130" s="17" t="inlineStr">
@@ -7505,7 +7525,7 @@
       </c>
       <c r="I130" s="17" t="inlineStr">
         <is>
-          <t>Confidential / CJIS</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J130" s="15" t="inlineStr">
@@ -7515,7 +7535,7 @@
       </c>
       <c r="K130" s="17" t="inlineStr">
         <is>
-          <t>CJIS-mandated per-individual security-awareness training completion for everyone with access to CJIS-regulated systems, with dates. Distinct from general training records; what auditors request. Built alongside AUP acknowledgment.</t>
+          <t>Dated verification that cameras, badge readers, and door sensors are functioning and recording correctly, with retention settings confirmed and faults remediated.</t>
         </is>
       </c>
       <c r="L130" s="17" t="n"/>
@@ -7533,29 +7553,33 @@
       </c>
       <c r="C131" s="15" t="inlineStr">
         <is>
-          <t>T4-41</t>
+          <t>T4-40</t>
         </is>
       </c>
       <c r="D131" s="16" t="inlineStr">
         <is>
-          <t>A-157</t>
+          <t>A-026</t>
         </is>
       </c>
       <c r="E131" s="15" t="n"/>
-      <c r="F131" s="15" t="n"/>
+      <c r="F131" s="15" t="inlineStr">
+        <is>
+          <t>A-086</t>
+        </is>
+      </c>
       <c r="G131" s="17" t="inlineStr">
         <is>
-          <t>Supply Chain Security Policy</t>
+          <t>CJIS Security Awareness Training Completion Record</t>
         </is>
       </c>
       <c r="H131" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I131" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Confidential / CJIS</t>
         </is>
       </c>
       <c r="J131" s="15" t="inlineStr">
@@ -7565,7 +7589,7 @@
       </c>
       <c r="K131" s="17" t="inlineStr">
         <is>
-          <t>Requires assessing each supplier's security posture, threat vectors, and integration risk before approving new systems, software, or hardware, and governs delivery validation. Defines procurement security review steps.</t>
+          <t>CJIS-mandated per-individual security-awareness training completion for everyone with access to CJIS-regulated systems, with dates. Distinct from general training records; what auditors request. Built alongside AUP acknowledgment.</t>
         </is>
       </c>
       <c r="L131" s="17" t="n"/>
@@ -7583,33 +7607,29 @@
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>T4-42</t>
+          <t>T4-41</t>
         </is>
       </c>
       <c r="D132" s="16" t="inlineStr">
         <is>
-          <t>A-159</t>
+          <t>A-157</t>
         </is>
       </c>
       <c r="E132" s="15" t="n"/>
-      <c r="F132" s="15" t="inlineStr">
-        <is>
-          <t>A-157</t>
-        </is>
-      </c>
+      <c r="F132" s="15" t="n"/>
       <c r="G132" s="17" t="inlineStr">
         <is>
-          <t>Approved Vendor / Product List</t>
+          <t>Supply Chain Security Policy</t>
         </is>
       </c>
       <c r="H132" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J132" s="15" t="inlineStr">
@@ -7619,7 +7639,7 @@
       </c>
       <c r="K132" s="17" t="inlineStr">
         <is>
-          <t>Approved suppliers and products for critical technology, with a deviation log for any procurement outside the list and its rationale.</t>
+          <t>Requires assessing each supplier's security posture, threat vectors, and integration risk before approving new systems, software, or hardware, and governs delivery validation. Defines procurement security review steps.</t>
         </is>
       </c>
       <c r="L132" s="17" t="n"/>
@@ -7637,12 +7657,12 @@
       </c>
       <c r="C133" s="15" t="inlineStr">
         <is>
-          <t>T4-43</t>
+          <t>T4-42</t>
         </is>
       </c>
       <c r="D133" s="16" t="inlineStr">
         <is>
-          <t>A-158</t>
+          <t>A-159</t>
         </is>
       </c>
       <c r="E133" s="15" t="n"/>
@@ -7653,17 +7673,17 @@
       </c>
       <c r="G133" s="17" t="inlineStr">
         <is>
-          <t>Hardware / Software Delivery Inspection Checklist</t>
+          <t>Approved Vendor / Product List</t>
         </is>
       </c>
       <c r="H133" s="17" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I133" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J133" s="15" t="inlineStr">
@@ -7673,7 +7693,7 @@
       </c>
       <c r="K133" s="17" t="inlineStr">
         <is>
-          <t>Verifies delivered technology is untampered and matches what was ordered, with enhanced validation of patches/updates (signature checks, hashes, sandbox testing) before production. Includes a chain-of-custody hand-off log (signed receipt and dispatch) for incoming and outgoing critical equipment.</t>
+          <t>Approved suppliers and products for critical technology, with a deviation log for any procurement outside the list and its rationale.</t>
         </is>
       </c>
       <c r="L133" s="17" t="n"/>
@@ -7686,38 +7706,38 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Tier 5</t>
+          <t>Tier 4</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>T5-01</t>
+          <t>T4-43</t>
         </is>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>A-133</t>
+          <t>A-158</t>
         </is>
       </c>
       <c r="E134" s="15" t="n"/>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>A-057</t>
+          <t>A-157</t>
         </is>
       </c>
       <c r="G134" s="17" t="inlineStr">
         <is>
-          <t>Continuous Monitoring Plan</t>
+          <t>Hardware / Software Delivery Inspection Checklist</t>
         </is>
       </c>
       <c r="H134" s="17" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="I134" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J134" s="15" t="inlineStr">
@@ -7727,7 +7747,7 @@
       </c>
       <c r="K134" s="17" t="inlineStr">
         <is>
-          <t>Defines monitoring scope, tools, alert thresholds, review cadence, and responsible personnel for CAD, GIS, call routing, and other platforms, including cloud/virtualized systems. Define the monitored scope explicitly; systems outside scope are coverage gaps, tracked as findings in the Risk / Finding Register.</t>
+          <t>Verifies delivered technology is untampered and matches what was ordered, with enhanced validation of patches/updates (signature checks, hashes, sandbox testing) before production. Includes a chain-of-custody hand-off log (signed receipt and dispatch) for incoming and outgoing critical equipment.</t>
         </is>
       </c>
       <c r="L134" s="17" t="n"/>
@@ -7745,28 +7765,28 @@
       </c>
       <c r="C135" s="15" t="inlineStr">
         <is>
-          <t>T5-02</t>
+          <t>T5-01</t>
         </is>
       </c>
       <c r="D135" s="16" t="inlineStr">
         <is>
-          <t>A-169</t>
+          <t>A-133</t>
         </is>
       </c>
       <c r="E135" s="15" t="n"/>
       <c r="F135" s="15" t="inlineStr">
         <is>
-          <t>A-014</t>
+          <t>A-057</t>
         </is>
       </c>
       <c r="G135" s="17" t="inlineStr">
         <is>
-          <t>TDoS / DoS Response Procedure</t>
+          <t>Continuous Monitoring Plan</t>
         </is>
       </c>
       <c r="H135" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="I135" s="17" t="inlineStr">
@@ -7781,7 +7801,7 @@
       </c>
       <c r="K135" s="17" t="inlineStr">
         <is>
-          <t>Detect, respond to, and maintain continuity during telephony and network denial-of-service: detection methods, upstream carrier coordination, call filtering, escalation contacts, and failover. Cross-references the IRP and the Backup Call-Handling / Dispatch Continuity Procedure.</t>
+          <t>Defines monitoring scope, tools, alert thresholds, review cadence, and responsible personnel for CAD, GIS, call routing, and other platforms, including cloud/virtualized systems. Define the monitored scope explicitly; systems outside scope are coverage gaps, tracked as findings in the Risk / Finding Register.</t>
         </is>
       </c>
       <c r="L135" s="17" t="n"/>
@@ -7799,12 +7819,12 @@
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>T5-03</t>
+          <t>T5-02</t>
         </is>
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>A-061</t>
+          <t>A-169</t>
         </is>
       </c>
       <c r="E136" s="15" t="n"/>
@@ -7815,17 +7835,17 @@
       </c>
       <c r="G136" s="17" t="inlineStr">
         <is>
-          <t>IRP Revision History / Update Log</t>
+          <t>TDoS / DoS Response Procedure</t>
         </is>
       </c>
       <c r="H136" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I136" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J136" s="15" t="inlineStr">
@@ -7835,7 +7855,7 @@
       </c>
       <c r="K136" s="17" t="inlineStr">
         <is>
-          <t>Version log of IRP changes in response to exercises, incidents, and environment changes: version, date, author, summary of change.</t>
+          <t>Detect, respond to, and maintain continuity during telephony and network denial-of-service: detection methods, upstream carrier coordination, call filtering, escalation contacts, and failover. Cross-references the IRP and the Backup Call-Handling / Dispatch Continuity Procedure.</t>
         </is>
       </c>
       <c r="L136" s="17" t="n"/>
@@ -7853,12 +7873,12 @@
       </c>
       <c r="C137" s="15" t="inlineStr">
         <is>
-          <t>T5-04</t>
+          <t>T5-03</t>
         </is>
       </c>
       <c r="D137" s="16" t="inlineStr">
         <is>
-          <t>A-168</t>
+          <t>A-061</t>
         </is>
       </c>
       <c r="E137" s="15" t="n"/>
@@ -7869,7 +7889,7 @@
       </c>
       <c r="G137" s="17" t="inlineStr">
         <is>
-          <t>Incident Log / Register</t>
+          <t>IRP Revision History / Update Log</t>
         </is>
       </c>
       <c r="H137" s="17" t="inlineStr">
@@ -7879,7 +7899,7 @@
       </c>
       <c r="I137" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J137" s="15" t="inlineStr">
@@ -7889,7 +7909,7 @@
       </c>
       <c r="K137" s="17" t="inlineStr">
         <is>
-          <t>Running chronological record of every cyber-related incident and outage at occurrence: type, time, systems affected, investigation, and status. Security and operational metadata only, no PII (supports the Restricted floor). Feeds the After-Action Reports and the Risk Register, and supports HEA 1169 two-business-day IOT reporting.</t>
+          <t>Version log of IRP changes in response to exercises, incidents, and environment changes: version, date, author, summary of change.</t>
         </is>
       </c>
       <c r="L137" s="17" t="n"/>
@@ -7907,12 +7927,12 @@
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>T5-05</t>
+          <t>T5-04</t>
         </is>
       </c>
       <c r="D138" s="16" t="inlineStr">
         <is>
-          <t>A-060</t>
+          <t>A-168</t>
         </is>
       </c>
       <c r="E138" s="15" t="n"/>
@@ -7923,17 +7943,17 @@
       </c>
       <c r="G138" s="17" t="inlineStr">
         <is>
-          <t>After-Action Reports</t>
+          <t>Incident Log / Register</t>
         </is>
       </c>
       <c r="H138" s="17" t="inlineStr">
         <is>
-          <t>Report / Assessment</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I138" s="17" t="inlineStr">
         <is>
-          <t>Restricted / CJIS</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J138" s="15" t="inlineStr">
@@ -7943,7 +7963,7 @@
       </c>
       <c r="K138" s="17" t="inlineStr">
         <is>
-          <t>Post-exercise and post-incident findings: what worked, what failed, and the corrective actions taken. Feeds the Risk Register and IRP revision history; draws incidents from the Incident Log / Register.</t>
+          <t>Running chronological record of every cyber-related incident and outage at occurrence: type, time, systems affected, investigation, and status. Security and operational metadata only, no PII (supports the Restricted floor). Feeds the After-Action Reports and the Risk Register, and supports HEA 1169 two-business-day IOT reporting.</t>
         </is>
       </c>
       <c r="L138" s="17" t="n"/>
@@ -7961,12 +7981,12 @@
       </c>
       <c r="C139" s="15" t="inlineStr">
         <is>
-          <t>T5-06</t>
+          <t>T5-05</t>
         </is>
       </c>
       <c r="D139" s="16" t="inlineStr">
         <is>
-          <t>A-141</t>
+          <t>A-060</t>
         </is>
       </c>
       <c r="E139" s="15" t="n"/>
@@ -7977,12 +7997,12 @@
       </c>
       <c r="G139" s="17" t="inlineStr">
         <is>
-          <t>Forensic Readiness Plan</t>
+          <t>After-Action Reports</t>
         </is>
       </c>
       <c r="H139" s="17" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Report / Assessment</t>
         </is>
       </c>
       <c r="I139" s="17" t="inlineStr">
@@ -7997,7 +8017,7 @@
       </c>
       <c r="K139" s="17" t="inlineStr">
         <is>
-          <t>How the PSAP is prepared to investigate: designated analysts (internal or contracted), secure evidence storage, isolated analysis environments (air-gapped/sandbox) for untrusted media, escalation paths, and authorities. The plan behind the forensic procedures.</t>
+          <t>Post-exercise and post-incident findings: what worked, what failed, and the corrective actions taken. Feeds the Risk Register and IRP revision history; draws incidents from the Incident Log / Register.</t>
         </is>
       </c>
       <c r="L139" s="17" t="n"/>
@@ -8015,28 +8035,28 @@
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>T5-07</t>
+          <t>T5-06</t>
         </is>
       </c>
       <c r="D140" s="16" t="inlineStr">
         <is>
-          <t>A-062</t>
+          <t>A-141</t>
         </is>
       </c>
       <c r="E140" s="15" t="n"/>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>A-141</t>
+          <t>A-014</t>
         </is>
       </c>
       <c r="G140" s="17" t="inlineStr">
         <is>
-          <t>Evidence Collection &amp; Chain-of-Custody Procedures</t>
+          <t>Forensic Readiness Plan</t>
         </is>
       </c>
       <c r="H140" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="I140" s="17" t="inlineStr">
@@ -8051,7 +8071,7 @@
       </c>
       <c r="K140" s="17" t="inlineStr">
         <is>
-          <t>Forensically sound collection and handling: isolating systems, collecting volatile and persistent logs, capturing disk/memory images, and documenting chain of custody for every item before remediation. Includes SBC session-recording capture.</t>
+          <t>How the PSAP is prepared to investigate: designated analysts (internal or contracted), secure evidence storage, isolated analysis environments (air-gapped/sandbox) for untrusted media, escalation paths, and authorities. The plan behind the forensic procedures.</t>
         </is>
       </c>
       <c r="L140" s="17" t="n"/>
@@ -8069,12 +8089,12 @@
       </c>
       <c r="C141" s="15" t="inlineStr">
         <is>
-          <t>T5-08</t>
+          <t>T5-07</t>
         </is>
       </c>
       <c r="D141" s="16" t="inlineStr">
         <is>
-          <t>A-064</t>
+          <t>A-062</t>
         </is>
       </c>
       <c r="E141" s="15" t="n"/>
@@ -8085,7 +8105,7 @@
       </c>
       <c r="G141" s="17" t="inlineStr">
         <is>
-          <t>System Isolation Procedure</t>
+          <t>Evidence Collection &amp; Chain-of-Custody Procedures</t>
         </is>
       </c>
       <c r="H141" s="17" t="inlineStr">
@@ -8095,7 +8115,7 @@
       </c>
       <c r="I141" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Restricted / CJIS</t>
         </is>
       </c>
       <c r="J141" s="15" t="inlineStr">
@@ -8105,7 +8125,7 @@
       </c>
       <c r="K141" s="17" t="inlineStr">
         <is>
-          <t>How to isolate a compromised system while preserving evidence and minimizing impact on continuing operations: network containment steps, what to capture first, and authorization.</t>
+          <t>Forensically sound collection and handling: isolating systems, collecting volatile and persistent logs, capturing disk/memory images, and documenting chain of custody for every item before remediation. Includes SBC session-recording capture.</t>
         </is>
       </c>
       <c r="L141" s="17" t="n"/>
@@ -8123,33 +8143,33 @@
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>T5-09</t>
+          <t>T5-08</t>
         </is>
       </c>
       <c r="D142" s="16" t="inlineStr">
         <is>
-          <t>A-063</t>
+          <t>A-064</t>
         </is>
       </c>
       <c r="E142" s="15" t="n"/>
       <c r="F142" s="15" t="inlineStr">
         <is>
-          <t>A-062</t>
+          <t>A-141</t>
         </is>
       </c>
       <c r="G142" s="17" t="inlineStr">
         <is>
-          <t>Evidence Preservation Checklist</t>
+          <t>System Isolation Procedure</t>
         </is>
       </c>
       <c r="H142" s="17" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I142" s="17" t="inlineStr">
         <is>
-          <t>Restricted / CJIS</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J142" s="15" t="inlineStr">
@@ -8159,7 +8179,7 @@
       </c>
       <c r="K142" s="17" t="inlineStr">
         <is>
-          <t>Step-by-step list for first responders to identify, collect, and preserve digital evidence in order, with sign-off. Operational companion to the chain-of-custody procedures.</t>
+          <t>How to isolate a compromised system while preserving evidence and minimizing impact on continuing operations: network containment steps, what to capture first, and authorization.</t>
         </is>
       </c>
       <c r="L142" s="17" t="n"/>
@@ -8177,33 +8197,33 @@
       </c>
       <c r="C143" s="15" t="inlineStr">
         <is>
-          <t>T5-10</t>
+          <t>T5-09</t>
         </is>
       </c>
       <c r="D143" s="16" t="inlineStr">
         <is>
-          <t>A-142</t>
+          <t>A-063</t>
         </is>
       </c>
       <c r="E143" s="15" t="n"/>
       <c r="F143" s="15" t="inlineStr">
         <is>
-          <t>A-141</t>
+          <t>A-062</t>
         </is>
       </c>
       <c r="G143" s="17" t="inlineStr">
         <is>
-          <t>Forensic Tool Inventory</t>
+          <t>Evidence Preservation Checklist</t>
         </is>
       </c>
       <c r="H143" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="I143" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Restricted / CJIS</t>
         </is>
       </c>
       <c r="J143" s="15" t="inlineStr">
@@ -8213,7 +8233,7 @@
       </c>
       <c r="K143" s="17" t="inlineStr">
         <is>
-          <t>Forensic tools available to the PSAP or its IT support, their purpose, and who is authorized to use them.</t>
+          <t>Step-by-step list for first responders to identify, collect, and preserve digital evidence in order, with sign-off. Operational companion to the chain-of-custody procedures.</t>
         </is>
       </c>
       <c r="L143" s="17" t="n"/>
@@ -8231,28 +8251,28 @@
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>T5-11</t>
+          <t>T5-10</t>
         </is>
       </c>
       <c r="D144" s="16" t="inlineStr">
         <is>
-          <t>A-046</t>
+          <t>A-142</t>
         </is>
       </c>
       <c r="E144" s="15" t="n"/>
       <c r="F144" s="15" t="inlineStr">
         <is>
-          <t>A-014</t>
+          <t>A-141</t>
         </is>
       </c>
       <c r="G144" s="17" t="inlineStr">
         <is>
-          <t>Unauthorized Disclosure Response &amp; Notification Procedures</t>
+          <t>Forensic Tool Inventory</t>
         </is>
       </c>
       <c r="H144" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I144" s="17" t="inlineStr">
@@ -8267,7 +8287,7 @@
       </c>
       <c r="K144" s="17" t="inlineStr">
         <is>
-          <t>Steps to detect, contain, investigate, and remediate an unauthorized data spill or disclosure, and to notify as required (Indiana AG and affected individuals under IC 24-4.9; IOT under HEA 1169). Triggers from the IRP for data-specific incidents.</t>
+          <t>Forensic tools available to the PSAP or its IT support, their purpose, and who is authorized to use them.</t>
         </is>
       </c>
       <c r="L144" s="17" t="n"/>
@@ -8285,23 +8305,23 @@
       </c>
       <c r="C145" s="15" t="inlineStr">
         <is>
-          <t>T5-12</t>
+          <t>T5-11</t>
         </is>
       </c>
       <c r="D145" s="16" t="inlineStr">
         <is>
-          <t>A-167</t>
+          <t>A-046</t>
         </is>
       </c>
       <c r="E145" s="15" t="n"/>
       <c r="F145" s="15" t="inlineStr">
         <is>
-          <t>A-012</t>
+          <t>A-014</t>
         </is>
       </c>
       <c r="G145" s="17" t="inlineStr">
         <is>
-          <t>Data Sharing &amp; Disclosure Approval Procedure</t>
+          <t>Unauthorized Disclosure Response &amp; Notification Procedures</t>
         </is>
       </c>
       <c r="H145" s="17" t="inlineStr">
@@ -8311,7 +8331,7 @@
       </c>
       <c r="I145" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J145" s="15" t="inlineStr">
@@ -8321,7 +8341,7 @@
       </c>
       <c r="K145" s="17" t="inlineStr">
         <is>
-          <t>Governs approval to share sensitive data: who approves a release, which risk factors apply (recipient, classification, legal triggers), and how approved data is securely transmitted. Distinct from the unauthorized-disclosure response. Produces a signed Data Sharing Agreement (MOU).</t>
+          <t>Steps to detect, contain, investigate, and remediate an unauthorized data spill or disclosure, and to notify as required (Indiana AG and affected individuals under IC 24-4.9; IOT under HEA 1169). Triggers from the IRP for data-specific incidents.</t>
         </is>
       </c>
       <c r="L145" s="17" t="n"/>
@@ -8339,28 +8359,28 @@
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>T5-13</t>
+          <t>T5-12</t>
         </is>
       </c>
       <c r="D146" s="16" t="inlineStr">
         <is>
-          <t>A-171</t>
+          <t>A-167</t>
         </is>
       </c>
       <c r="E146" s="15" t="n"/>
       <c r="F146" s="15" t="inlineStr">
         <is>
-          <t>A-167</t>
+          <t>A-012</t>
         </is>
       </c>
       <c r="G146" s="17" t="inlineStr">
         <is>
-          <t>Data Sharing Agreement (MOU) Template</t>
+          <t>Data Sharing &amp; Disclosure Approval Procedure</t>
         </is>
       </c>
       <c r="H146" s="17" t="inlineStr">
         <is>
-          <t>Agreement / Form</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I146" s="17" t="inlineStr">
@@ -8375,7 +8395,7 @@
       </c>
       <c r="K146" s="17" t="inlineStr">
         <is>
-          <t>The signed instrument executed when PSAP data is shared with a partner agency or third party: parties, data scope and classification, permitted use, handling and security obligations, retention, and signatures. Companion to the Data Sharing &amp; Disclosure Approval Procedure; retained per partner.</t>
+          <t>Governs approval to share sensitive data: who approves a release, which risk factors apply (recipient, classification, legal triggers), and how approved data is securely transmitted. Distinct from the unauthorized-disclosure response. Produces a signed Data Sharing Agreement (MOU).</t>
         </is>
       </c>
       <c r="L146" s="17" t="n"/>
@@ -8393,33 +8413,33 @@
       </c>
       <c r="C147" s="15" t="inlineStr">
         <is>
-          <t>T5-14</t>
+          <t>T5-13</t>
         </is>
       </c>
       <c r="D147" s="16" t="inlineStr">
         <is>
-          <t>A-097</t>
+          <t>A-171</t>
         </is>
       </c>
       <c r="E147" s="15" t="n"/>
       <c r="F147" s="15" t="inlineStr">
         <is>
-          <t>A-010</t>
+          <t>A-167</t>
         </is>
       </c>
       <c r="G147" s="17" t="inlineStr">
         <is>
-          <t>Session Management Policy</t>
+          <t>Data Sharing Agreement (MOU) Template</t>
         </is>
       </c>
       <c r="H147" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Agreement / Form</t>
         </is>
       </c>
       <c r="I147" s="17" t="inlineStr">
         <is>
-          <t>Internal / CJIS</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J147" s="15" t="inlineStr">
@@ -8429,7 +8449,7 @@
       </c>
       <c r="K147" s="17" t="inlineStr">
         <is>
-          <t>Sets session rules: individual authentication before every session (no shared accounts) so each session traces to one person, idle lock/terminate timeouts by system type, reauthentication for higher-risk actions, and termination on disconnect or failed periodic checks. Covers workstations and remote devices.</t>
+          <t>The signed instrument executed when PSAP data is shared with a partner agency or third party: parties, data scope and classification, permitted use, handling and security obligations, retention, and signatures. Companion to the Data Sharing &amp; Disclosure Approval Procedure; retained per partner.</t>
         </is>
       </c>
       <c r="L147" s="17" t="n"/>
@@ -8447,23 +8467,23 @@
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>T5-15</t>
+          <t>T5-14</t>
         </is>
       </c>
       <c r="D148" s="16" t="inlineStr">
         <is>
-          <t>A-105</t>
+          <t>A-097</t>
         </is>
       </c>
       <c r="E148" s="15" t="n"/>
       <c r="F148" s="15" t="inlineStr">
         <is>
-          <t>A-047</t>
+          <t>A-010</t>
         </is>
       </c>
       <c r="G148" s="17" t="inlineStr">
         <is>
-          <t>Network Monitoring Policy</t>
+          <t>Session Management Policy</t>
         </is>
       </c>
       <c r="H148" s="17" t="inlineStr">
@@ -8473,7 +8493,7 @@
       </c>
       <c r="I148" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal / CJIS</t>
         </is>
       </c>
       <c r="J148" s="15" t="inlineStr">
@@ -8483,7 +8503,7 @@
       </c>
       <c r="K148" s="17" t="inlineStr">
         <is>
-          <t>Defines what traffic is monitored, what constitutes an alert, who is notified, and the default-deny and rate-limiting/traffic-shaping controls (including DoS resource-exhaustion defenses and their testing). Governs IDS/IPS use and device-to-device control. DoS response and continuity sit in the TDoS / DoS Response Procedure.</t>
+          <t>Sets session rules: individual authentication before every session (no shared accounts) so each session traces to one person, idle lock/terminate timeouts by system type, reauthentication for higher-risk actions, and termination on disconnect or failed periodic checks. Covers workstations and remote devices.</t>
         </is>
       </c>
       <c r="L148" s="17" t="n"/>
@@ -8501,19 +8521,23 @@
       </c>
       <c r="C149" s="15" t="inlineStr">
         <is>
-          <t>T5-16</t>
+          <t>T5-15</t>
         </is>
       </c>
       <c r="D149" s="16" t="inlineStr">
         <is>
-          <t>A-109</t>
+          <t>A-105</t>
         </is>
       </c>
       <c r="E149" s="15" t="n"/>
-      <c r="F149" s="15" t="n"/>
+      <c r="F149" s="15" t="inlineStr">
+        <is>
+          <t>A-047</t>
+        </is>
+      </c>
       <c r="G149" s="17" t="inlineStr">
         <is>
-          <t>DNS Filtering Policy</t>
+          <t>Network Monitoring Policy</t>
         </is>
       </c>
       <c r="H149" s="17" t="inlineStr">
@@ -8533,7 +8557,7 @@
       </c>
       <c r="K149" s="17" t="inlineStr">
         <is>
-          <t>Governs protective DNS filtering: blocked categories, allow/deny handling, and review. Scoped to filtering; DNS administration and change governance live in the Change Management Policy and the DNS Security Configuration Record.</t>
+          <t>Defines what traffic is monitored, what constitutes an alert, who is notified, and the default-deny and rate-limiting/traffic-shaping controls (including DoS resource-exhaustion defenses and their testing). Governs IDS/IPS use and device-to-device control. DoS response and continuity sit in the TDoS / DoS Response Procedure.</t>
         </is>
       </c>
       <c r="L149" s="17" t="n"/>
@@ -8551,33 +8575,29 @@
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>T5-17</t>
+          <t>T5-16</t>
         </is>
       </c>
       <c r="D150" s="16" t="inlineStr">
         <is>
-          <t>A-108</t>
+          <t>A-109</t>
         </is>
       </c>
       <c r="E150" s="15" t="n"/>
-      <c r="F150" s="15" t="inlineStr">
-        <is>
-          <t>A-047</t>
-        </is>
-      </c>
+      <c r="F150" s="15" t="n"/>
       <c r="G150" s="17" t="inlineStr">
         <is>
-          <t>DNS Security Configuration Record</t>
+          <t>DNS Filtering Policy</t>
         </is>
       </c>
       <c r="H150" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I150" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J150" s="15" t="inlineStr">
@@ -8587,7 +8607,7 @@
       </c>
       <c r="K150" s="17" t="inlineStr">
         <is>
-          <t>As-built DNS security: separation of authoritative and recursive services, DNSSEC or encrypted DNS, the secure configuration baseline (disabled risky features, input validation), MFA for DNS admins, and DNS query/change logging into the SIEM. DNS change governance runs through the Change Management Policy.</t>
+          <t>Governs protective DNS filtering: blocked categories, allow/deny handling, and review. Scoped to filtering; DNS administration and change governance live in the Change Management Policy and the DNS Security Configuration Record.</t>
         </is>
       </c>
       <c r="L150" s="17" t="n"/>
@@ -8605,29 +8625,33 @@
       </c>
       <c r="C151" s="15" t="inlineStr">
         <is>
-          <t>T5-18</t>
+          <t>T5-17</t>
         </is>
       </c>
       <c r="D151" s="16" t="inlineStr">
         <is>
-          <t>A-049</t>
+          <t>A-108</t>
         </is>
       </c>
       <c r="E151" s="15" t="n"/>
-      <c r="F151" s="15" t="n"/>
+      <c r="F151" s="15" t="inlineStr">
+        <is>
+          <t>A-047</t>
+        </is>
+      </c>
       <c r="G151" s="17" t="inlineStr">
         <is>
-          <t>Email Security Policy</t>
+          <t>DNS Security Configuration Record</t>
         </is>
       </c>
       <c r="H151" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I151" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J151" s="15" t="inlineStr">
@@ -8637,7 +8661,7 @@
       </c>
       <c r="K151" s="17" t="inlineStr">
         <is>
-          <t>Treats email as a semi-trusted system isolated from real-time operations: acceptable use, external-email and link/attachment handling, mailbox-delegation and inbox-rule restrictions to approved staff, and the inspection/sandboxing expected. Defines reporting of suspicious email.</t>
+          <t>As-built DNS security: separation of authoritative and recursive services, DNSSEC or encrypted DNS, the secure configuration baseline (disabled risky features, input validation), MFA for DNS admins, and DNS query/change logging into the SIEM. DNS change governance runs through the Change Management Policy.</t>
         </is>
       </c>
       <c r="L151" s="17" t="n"/>
@@ -8655,28 +8679,24 @@
       </c>
       <c r="C152" s="15" t="inlineStr">
         <is>
-          <t>T5-19</t>
+          <t>T5-18</t>
         </is>
       </c>
       <c r="D152" s="16" t="inlineStr">
         <is>
-          <t>A-110</t>
+          <t>A-049</t>
         </is>
       </c>
       <c r="E152" s="15" t="n"/>
-      <c r="F152" s="15" t="inlineStr">
-        <is>
-          <t>A-049</t>
-        </is>
-      </c>
+      <c r="F152" s="15" t="n"/>
       <c r="G152" s="17" t="inlineStr">
         <is>
-          <t>Email Authentication Configuration Records (SPF/DKIM/DMARC)</t>
+          <t>Email Security Policy</t>
         </is>
       </c>
       <c r="H152" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I152" s="17" t="inlineStr">
@@ -8691,7 +8711,7 @@
       </c>
       <c r="K152" s="17" t="inlineStr">
         <is>
-          <t>As-built email authentication: SPF, DKIM, DMARC, and TLS settings, with the audit cadence for these settings. Implements the Email Security Policy.</t>
+          <t>Treats email as a semi-trusted system isolated from real-time operations: acceptable use, external-email and link/attachment handling, mailbox-delegation and inbox-rule restrictions to approved staff, and the inspection/sandboxing expected. Defines reporting of suspicious email.</t>
         </is>
       </c>
       <c r="L152" s="17" t="n"/>
@@ -8709,12 +8729,12 @@
       </c>
       <c r="C153" s="15" t="inlineStr">
         <is>
-          <t>T5-20</t>
+          <t>T5-19</t>
         </is>
       </c>
       <c r="D153" s="16" t="inlineStr">
         <is>
-          <t>A-111</t>
+          <t>A-110</t>
         </is>
       </c>
       <c r="E153" s="15" t="n"/>
@@ -8725,7 +8745,7 @@
       </c>
       <c r="G153" s="17" t="inlineStr">
         <is>
-          <t>Anti-Phishing / Spam Filter Configuration Records</t>
+          <t>Email Authentication Configuration Records (SPF/DKIM/DMARC)</t>
         </is>
       </c>
       <c r="H153" s="17" t="inlineStr">
@@ -8735,7 +8755,7 @@
       </c>
       <c r="I153" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J153" s="15" t="inlineStr">
@@ -8745,7 +8765,7 @@
       </c>
       <c r="K153" s="17" t="inlineStr">
         <is>
-          <t>As-built mail filtering: anti-spam and anti-phishing tooling, attachment/link scanning and sandboxing, and the alerting that flags or blocks malicious mail.</t>
+          <t>As-built email authentication: SPF, DKIM, DMARC, and TLS settings, with the audit cadence for these settings. Implements the Email Security Policy.</t>
         </is>
       </c>
       <c r="L153" s="17" t="n"/>
@@ -8763,29 +8783,33 @@
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>T5-21</t>
+          <t>T5-20</t>
         </is>
       </c>
       <c r="D154" s="16" t="inlineStr">
         <is>
-          <t>A-112</t>
+          <t>A-111</t>
         </is>
       </c>
       <c r="E154" s="15" t="n"/>
-      <c r="F154" s="15" t="n"/>
+      <c r="F154" s="15" t="inlineStr">
+        <is>
+          <t>A-049</t>
+        </is>
+      </c>
       <c r="G154" s="17" t="inlineStr">
         <is>
-          <t>Wireless Network Policy</t>
+          <t>Anti-Phishing / Spam Filter Configuration Records</t>
         </is>
       </c>
       <c r="H154" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I154" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J154" s="15" t="inlineStr">
@@ -8795,7 +8819,7 @@
       </c>
       <c r="K154" s="17" t="inlineStr">
         <is>
-          <t>Authorizes all wireless networks and sets encryption (WPA3 or minimum WPA2-Enterprise), authentication, SSID segregation, guest-network controls, prohibited devices, and limits admin functions to trained staff. Covers field-deployed and cellular links.</t>
+          <t>As-built mail filtering: anti-spam and anti-phishing tooling, attachment/link scanning and sandboxing, and the alerting that flags or blocks malicious mail.</t>
         </is>
       </c>
       <c r="L154" s="17" t="n"/>
@@ -8813,28 +8837,24 @@
       </c>
       <c r="C155" s="15" t="inlineStr">
         <is>
-          <t>T5-22</t>
+          <t>T5-21</t>
         </is>
       </c>
       <c r="D155" s="16" t="inlineStr">
         <is>
-          <t>A-114</t>
+          <t>A-112</t>
         </is>
       </c>
       <c r="E155" s="15" t="n"/>
-      <c r="F155" s="15" t="inlineStr">
-        <is>
-          <t>A-112</t>
-        </is>
-      </c>
+      <c r="F155" s="15" t="n"/>
       <c r="G155" s="17" t="inlineStr">
         <is>
-          <t>Cellular / Mobile Device Security Standards</t>
+          <t>Wireless Network Policy</t>
         </is>
       </c>
       <c r="H155" s="17" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I155" s="17" t="inlineStr">
@@ -8849,7 +8869,7 @@
       </c>
       <c r="K155" s="17" t="inlineStr">
         <is>
-          <t>Security requirements for cellular access to emergency-services applications: MDM or private-APN management, disable-when-idle, restriction to mission-essential services, encryption of cellular/broadband sessions (VPN or app-level), and rogue-base-station detection.</t>
+          <t>Authorizes all wireless networks and sets encryption (WPA3 or minimum WPA2-Enterprise), authentication, SSID segregation, guest-network controls, prohibited devices, and limits admin functions to trained staff. Covers field-deployed and cellular links.</t>
         </is>
       </c>
       <c r="L155" s="17" t="n"/>
@@ -8867,12 +8887,12 @@
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>T5-23</t>
+          <t>T5-22</t>
         </is>
       </c>
       <c r="D156" s="16" t="inlineStr">
         <is>
-          <t>A-113</t>
+          <t>A-114</t>
         </is>
       </c>
       <c r="E156" s="15" t="n"/>
@@ -8883,17 +8903,17 @@
       </c>
       <c r="G156" s="17" t="inlineStr">
         <is>
-          <t>Wireless Network Inventory</t>
+          <t>Cellular / Mobile Device Security Standards</t>
         </is>
       </c>
       <c r="H156" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I156" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J156" s="15" t="inlineStr">
@@ -8903,7 +8923,7 @@
       </c>
       <c r="K156" s="17" t="inlineStr">
         <is>
-          <t>All authorized access points, SSIDs, and associated network segments, with their configuration baseline. Reconciled and audited on a set cadence.</t>
+          <t>Security requirements for cellular access to emergency-services applications: MDM or private-APN management, disable-when-idle, restriction to mission-essential services, encryption of cellular/broadband sessions (VPN or app-level), and rogue-base-station detection.</t>
         </is>
       </c>
       <c r="L156" s="17" t="n"/>
@@ -8921,29 +8941,33 @@
       </c>
       <c r="C157" s="15" t="inlineStr">
         <is>
-          <t>T5-24</t>
+          <t>T5-23</t>
         </is>
       </c>
       <c r="D157" s="16" t="inlineStr">
         <is>
-          <t>A-123</t>
+          <t>A-113</t>
         </is>
       </c>
       <c r="E157" s="15" t="n"/>
-      <c r="F157" s="15" t="n"/>
+      <c r="F157" s="15" t="inlineStr">
+        <is>
+          <t>A-112</t>
+        </is>
+      </c>
       <c r="G157" s="17" t="inlineStr">
         <is>
-          <t>Mobile Device Management (MDM) Policy</t>
+          <t>Wireless Network Inventory</t>
         </is>
       </c>
       <c r="H157" s="17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I157" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J157" s="15" t="inlineStr">
@@ -8953,7 +8977,7 @@
       </c>
       <c r="K157" s="17" t="inlineStr">
         <is>
-          <t>Rules for mobile and remote devices accessing PSAP systems: on-device encryption, strong login (MFA or certificates), remote-wipe, data-leakage controls, acceptable use, and ownership. Enforced via MDM; compliance checked on a set cadence.</t>
+          <t>All authorized access points, SSIDs, and associated network segments, with their configuration baseline. Reconciled and audited on a set cadence.</t>
         </is>
       </c>
       <c r="L157" s="17" t="n"/>
@@ -8971,33 +8995,29 @@
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>T5-25</t>
+          <t>T5-24</t>
         </is>
       </c>
       <c r="D158" s="16" t="inlineStr">
         <is>
-          <t>A-116</t>
+          <t>A-123</t>
         </is>
       </c>
       <c r="E158" s="15" t="n"/>
-      <c r="F158" s="15" t="inlineStr">
-        <is>
-          <t>A-050</t>
-        </is>
-      </c>
+      <c r="F158" s="15" t="n"/>
       <c r="G158" s="17" t="inlineStr">
         <is>
-          <t>Authorized Remote Device Register</t>
+          <t>Mobile Device Management (MDM) Policy</t>
         </is>
       </c>
       <c r="H158" s="17" t="inlineStr">
         <is>
-          <t>Inventory / Register</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="I158" s="17" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="J158" s="15" t="inlineStr">
@@ -9007,7 +9027,7 @@
       </c>
       <c r="K158" s="17" t="inlineStr">
         <is>
-          <t>Every individual and vendor account with remote-access rights, the approval date, and access scope. Reconciled periodically to confirm all active remote access remains authorized.</t>
+          <t>Rules for mobile and remote devices accessing PSAP systems: on-device encryption, strong login (MFA or certificates), remote-wipe, data-leakage controls, acceptable use, and ownership. Enforced via MDM; compliance checked on a set cadence.</t>
         </is>
       </c>
       <c r="L158" s="17" t="n"/>
@@ -9025,12 +9045,12 @@
       </c>
       <c r="C159" s="15" t="inlineStr">
         <is>
-          <t>T5-26</t>
+          <t>T5-25</t>
         </is>
       </c>
       <c r="D159" s="16" t="inlineStr">
         <is>
-          <t>A-115</t>
+          <t>A-116</t>
         </is>
       </c>
       <c r="E159" s="15" t="n"/>
@@ -9041,12 +9061,12 @@
       </c>
       <c r="G159" s="17" t="inlineStr">
         <is>
-          <t>VPN / Remote Access Configuration Records</t>
+          <t>Authorized Remote Device Register</t>
         </is>
       </c>
       <c r="H159" s="17" t="inlineStr">
         <is>
-          <t>Configuration Record</t>
+          <t>Inventory / Register</t>
         </is>
       </c>
       <c r="I159" s="17" t="inlineStr">
@@ -9061,7 +9081,7 @@
       </c>
       <c r="K159" s="17" t="inlineStr">
         <is>
-          <t>As-built remote access: approved tools, authentication (MFA, key-based SSH, approved ciphers), split-tunneling stance, and session controls (device attestation, disconnect on VPN drop). Implements the Remote Access Policy.</t>
+          <t>Every individual and vendor account with remote-access rights, the approval date, and access scope. Reconciled periodically to confirm all active remote access remains authorized.</t>
         </is>
       </c>
       <c r="L159" s="17" t="n"/>
@@ -9079,24 +9099,28 @@
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>T5-27</t>
+          <t>T5-26</t>
         </is>
       </c>
       <c r="D160" s="16" t="inlineStr">
         <is>
-          <t>A-170</t>
+          <t>A-115</t>
         </is>
       </c>
       <c r="E160" s="15" t="n"/>
-      <c r="F160" s="15" t="n"/>
+      <c r="F160" s="15" t="inlineStr">
+        <is>
+          <t>A-050</t>
+        </is>
+      </c>
       <c r="G160" s="17" t="inlineStr">
         <is>
-          <t>Multimedia &amp; File Ingestion Sanitization Procedure</t>
+          <t>VPN / Remote Access Configuration Records</t>
         </is>
       </c>
       <c r="H160" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Configuration Record</t>
         </is>
       </c>
       <c r="I160" s="17" t="inlineStr">
@@ -9111,7 +9135,7 @@
       </c>
       <c r="K160" s="17" t="inlineStr">
         <is>
-          <t>Sanitizes ingested multimedia and files (images, video, audio, MMS): malware scanning, format validation, metadata stripping, injection prevention, and privacy handling. NG911-specific intake controls beyond endpoint AV and email filtering.</t>
+          <t>As-built remote access: approved tools, authentication (MFA, key-based SSH, approved ciphers), split-tunneling stance, and session controls (device attestation, disconnect on VPN drop). Implements the Remote Access Policy.</t>
         </is>
       </c>
       <c r="L160" s="17" t="n"/>
@@ -9129,28 +9153,24 @@
       </c>
       <c r="C161" s="15" t="inlineStr">
         <is>
-          <t>T5-28</t>
+          <t>T5-27</t>
         </is>
       </c>
       <c r="D161" s="16" t="inlineStr">
         <is>
-          <t>A-124</t>
+          <t>A-170</t>
         </is>
       </c>
       <c r="E161" s="15" t="n"/>
-      <c r="F161" s="15" t="inlineStr">
-        <is>
-          <t>A-123</t>
-        </is>
-      </c>
+      <c r="F161" s="15" t="n"/>
       <c r="G161" s="17" t="inlineStr">
         <is>
-          <t>Remote Endpoint Security Audit Records</t>
+          <t>Multimedia &amp; File Ingestion Sanitization Procedure</t>
         </is>
       </c>
       <c r="H161" s="17" t="inlineStr">
         <is>
-          <t>Log / Record</t>
+          <t>Procedure</t>
         </is>
       </c>
       <c r="I161" s="17" t="inlineStr">
@@ -9165,7 +9185,7 @@
       </c>
       <c r="K161" s="17" t="inlineStr">
         <is>
-          <t>Dated evidence that remote and on-site endpoints feed logs centrally, sit behind the right network zones, and run current protections (patching, endpoint agents); records audit findings and remediation.</t>
+          <t>Sanitizes ingested multimedia and files (images, video, audio, MMS): malware scanning, format validation, metadata stripping, injection prevention, and privacy handling. NG911-specific intake controls beyond endpoint AV and email filtering.</t>
         </is>
       </c>
       <c r="L161" s="17" t="n"/>
@@ -9178,38 +9198,38 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Tier 6</t>
+          <t>Tier 5</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>T6-01</t>
+          <t>T5-28</t>
         </is>
       </c>
       <c r="D162" s="16" t="inlineStr">
         <is>
-          <t>A-085</t>
+          <t>A-124</t>
         </is>
       </c>
       <c r="E162" s="15" t="n"/>
       <c r="F162" s="15" t="inlineStr">
         <is>
-          <t>A-083</t>
+          <t>A-123</t>
         </is>
       </c>
       <c r="G162" s="17" t="inlineStr">
         <is>
-          <t>Issue Escalation Procedure</t>
+          <t>Remote Endpoint Security Audit Records</t>
         </is>
       </c>
       <c r="H162" s="17" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Log / Record</t>
         </is>
       </c>
       <c r="I162" s="17" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="J162" s="15" t="inlineStr">
@@ -9219,7 +9239,7 @@
       </c>
       <c r="K162" s="17" t="inlineStr">
         <is>
-          <t>When and how unresolved or overdue findings are escalated to leadership: thresholds, paths, and timing. Operates on the Risk / Finding Register, distinct from real-time alert escalation.</t>
+          <t>Dated evidence that remote and on-site endpoints feed logs centrally, sit behind the right network zones, and run current protections (patching, endpoint agents); records audit findings and remediation.</t>
         </is>
       </c>
       <c r="L162" s="17" t="n"/>
@@ -9237,46 +9257,100 @@
       </c>
       <c r="C163" s="15" t="inlineStr">
         <is>
-          <t>T6-02</t>
+          <t>T6-01</t>
         </is>
       </c>
       <c r="D163" s="16" t="inlineStr">
         <is>
-          <t>A-136</t>
+          <t>A-085</t>
         </is>
       </c>
       <c r="E163" s="15" t="n"/>
       <c r="F163" s="15" t="inlineStr">
         <is>
+          <t>A-083</t>
+        </is>
+      </c>
+      <c r="G163" s="17" t="inlineStr">
+        <is>
+          <t>Issue Escalation Procedure</t>
+        </is>
+      </c>
+      <c r="H163" s="17" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="I163" s="17" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="J163" s="15" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K163" s="17" t="inlineStr">
+        <is>
+          <t>When and how unresolved or overdue findings are escalated to leadership: thresholds, paths, and timing. Operates on the Risk / Finding Register, distinct from real-time alert escalation.</t>
+        </is>
+      </c>
+      <c r="L163" s="17" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="15" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B164" s="15" t="inlineStr">
+        <is>
+          <t>Tier 6</t>
+        </is>
+      </c>
+      <c r="C164" s="15" t="inlineStr">
+        <is>
+          <t>T6-02</t>
+        </is>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>A-136</t>
+        </is>
+      </c>
+      <c r="E164" s="15" t="n"/>
+      <c r="F164" s="15" t="inlineStr">
+        <is>
           <t>A-057</t>
         </is>
       </c>
-      <c r="G163" s="17" t="inlineStr">
+      <c r="G164" s="17" t="inlineStr">
         <is>
           <t>Security Event Review Procedures</t>
         </is>
       </c>
-      <c r="H163" s="17" t="inlineStr">
+      <c r="H164" s="17" t="inlineStr">
         <is>
           <t>Procedure</t>
         </is>
       </c>
-      <c r="I163" s="17" t="inlineStr">
+      <c r="I164" s="17" t="inlineStr">
         <is>
           <t>Restricted</t>
         </is>
       </c>
-      <c r="J163" s="15" t="inlineStr">
+      <c r="J164" s="15" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K163" s="17" t="inlineStr">
+      <c r="K164" s="17" t="inlineStr">
         <is>
           <t>Scheduled review of aggregated security-event data beyond individual alerts: cadence, what reviewers look for (logins, file access, config changes, intrusion indicators), and how anomalies affecting emergency operations are investigated and escalated. Governs the event-review meeting.</t>
         </is>
       </c>
-      <c r="L163" s="17" t="n"/>
+      <c r="L164" s="17" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L163"/>
@@ -9284,7 +9358,7 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J3:J163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J3:J164" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,Plan,Draft - In Progress,Draft - Complete,In Review,Final"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9397,7 +9471,7 @@
         <is>
           <t>A-001 — Cybersecurity Charter / Leadership Designation Letter
 A-002 — Cybersecurity &amp; Privacy Policy  (1.B)
-A-032 — Risk Management Methodology Document  (1.D)</t>
+A-032 — Risk Management Methodology Standard  (1.D)</t>
         </is>
       </c>
       <c r="G4" s="19" t="inlineStr">
@@ -9830,8 +9904,9 @@
           <t>A-117 — System Configuration Baselines (per system type)  (5.A)
 A-057 — Logging Policy  (7.A)
 A-014 — Incident Response Plan (IRP)  (8.A)
-A-032 — Risk Management Methodology Document  (1.D)
-A-083 — Risk / Finding Register (POA&amp;M)  (12.B)</t>
+A-032 — Risk Management Methodology Standard  (1.D)
+A-083 — Risk / Finding Register (POA&amp;M)  (12.B)
+A-172 — Risk Assessment Procedure  (1.D)</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
@@ -9841,7 +9916,7 @@
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>Spans 5.A/7.A/8.A/1.D/12.A. Confirm the bundle of procedures collectively satisfies this multi-part question.</t>
+          <t>Spans 5.A/7.A/8.A/1.D/12.A. Confirm the bundle of procedures collectively satisfies this multi-part question. A-172 added 2026-06-03 as the risk-assessment procedure in the bundle.</t>
         </is>
       </c>
     </row>
@@ -9873,7 +9948,7 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>A-032 — Risk Management Methodology Document</t>
+          <t>A-032 — Risk Management Methodology Standard</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -9958,7 +10033,7 @@
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>A-032 — Risk Management Methodology Document</t>
+          <t>A-172 — Risk Assessment Procedure</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -9968,7 +10043,7 @@
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>Confirmed: Risk Management Methodology Document serves as the SOP.</t>
+          <t>Remapped 2026-06-03 from A-032 to A-172 (Risk Assessment Procedure): the SOP is now the Procedure, not the Standard.</t>
         </is>
       </c>
     </row>
@@ -18299,7 +18374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18368,7 +18443,7 @@
         </is>
       </c>
       <c r="C4" s="17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
@@ -18458,7 +18533,7 @@
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -18488,7 +18563,7 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -18518,7 +18593,7 @@
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -18773,6 +18848,66 @@
       <c r="F17" s="17" t="inlineStr">
         <is>
           <t>Raise to Restricted if the matrix reveals system criticality rankings or operational security architecture (e.g., RTO/RPO matrix).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Financial Ledger</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Header (owner, coverage/cycle) | Ledger columns (entry #, fiscal cycle, line item/category, committed amount, funding source, notes) | Summary | Sign-off block | Retention note</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>Raise to Restricted if entries reveal security tooling spend that maps to defensive capability; raise to Confidential if entries carry individual salary detail or name people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Meeting Minutes</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Header (authority, owner, version, classification) | Meeting identification | Attendees | Topics reviewed | Decisions &amp; priorities | Action items | Sign-off block | Retention note</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>Raise to Confidential when entries carry PII beyond attendee names, or capture sensitive incident detail.</t>
         </is>
       </c>
     </row>
